--- a/research/traditional_assets/database/data/jordan/jordan_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_retail_automotive.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1107065751861337</v>
+        <v>0.1105211620357614</v>
       </c>
       <c r="C2">
-        <v>470.3965739627947</v>
+        <v>466.8092553287618</v>
       </c>
       <c r="D2">
-        <v>457.4965739627947</v>
+        <v>458.3432553287619</v>
       </c>
       <c r="E2">
-        <v>-200</v>
+        <v>-195.566</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.434</v>
       </c>
       <c r="G2">
         <v>12.9</v>
@@ -1451,28 +1451,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2230302</v>
       </c>
       <c r="N2">
-        <v>89.47499999999999</v>
+        <v>89.2519698</v>
       </c>
       <c r="O2">
-        <v>17.895</v>
+        <v>17.85039396</v>
       </c>
       <c r="P2">
-        <v>71.58</v>
+        <v>71.40157583999999</v>
       </c>
       <c r="Q2">
-        <v>73.23</v>
+        <v>73.05157584</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1107065751861337</v>
+        <v>0.1112310727633954</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7164970653807063</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>401.1788538054488</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1105211620357614</v>
+        <v>0.1103357488853891</v>
       </c>
       <c r="C3">
-        <v>466.8092553287618</v>
+        <v>463.2250763837868</v>
       </c>
       <c r="D3">
-        <v>458.3432553287619</v>
+        <v>459.1930763837868</v>
       </c>
       <c r="E3">
-        <v>-195.566</v>
+        <v>-191.132</v>
       </c>
       <c r="F3">
-        <v>4.434</v>
+        <v>8.868</v>
       </c>
       <c r="G3">
         <v>12.9</v>
@@ -1533,28 +1533,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M3">
-        <v>0.2230302</v>
+        <v>0.4460604</v>
       </c>
       <c r="N3">
-        <v>89.2519698</v>
+        <v>89.0289396</v>
       </c>
       <c r="O3">
-        <v>17.85039396</v>
+        <v>17.80578792</v>
       </c>
       <c r="P3">
-        <v>71.40157583999999</v>
+        <v>71.22315168</v>
       </c>
       <c r="Q3">
-        <v>73.05157584</v>
+        <v>72.87315168000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1112310727633954</v>
+        <v>0.1117662743728461</v>
       </c>
       <c r="T3">
-        <v>0.7164970653807063</v>
+        <v>0.7223577423704466</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>401.1788538054488</v>
+        <v>200.5894269027244</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1103357488853891</v>
+        <v>0.1101503357350169</v>
       </c>
       <c r="C4">
-        <v>463.2250763837868</v>
+        <v>459.6440546243422</v>
       </c>
       <c r="D4">
-        <v>459.1930763837868</v>
+        <v>460.0460546243422</v>
       </c>
       <c r="E4">
-        <v>-191.132</v>
+        <v>-186.698</v>
       </c>
       <c r="F4">
-        <v>8.868</v>
+        <v>13.302</v>
       </c>
       <c r="G4">
         <v>12.9</v>
@@ -1615,28 +1615,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M4">
-        <v>0.4460604</v>
+        <v>0.6690906</v>
       </c>
       <c r="N4">
-        <v>89.0289396</v>
+        <v>88.80590939999999</v>
       </c>
       <c r="O4">
-        <v>17.80578792</v>
+        <v>17.76118188</v>
       </c>
       <c r="P4">
-        <v>71.22315168</v>
+        <v>71.04472752</v>
       </c>
       <c r="Q4">
-        <v>72.87315168000001</v>
+        <v>72.69472752</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1117662743728461</v>
+        <v>0.1123125110670277</v>
       </c>
       <c r="T4">
-        <v>0.7223577423704466</v>
+        <v>0.7283392580610063</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>200.5894269027244</v>
+        <v>133.7262846018162</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1101503357350169</v>
+        <v>0.1099649225846446</v>
       </c>
       <c r="C5">
-        <v>459.6440546243422</v>
+        <v>456.0662076771467</v>
       </c>
       <c r="D5">
-        <v>460.0460546243422</v>
+        <v>460.9022076771467</v>
       </c>
       <c r="E5">
-        <v>-186.698</v>
+        <v>-182.264</v>
       </c>
       <c r="F5">
-        <v>13.302</v>
+        <v>17.736</v>
       </c>
       <c r="G5">
         <v>12.9</v>
@@ -1697,28 +1697,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M5">
-        <v>0.6690906</v>
+        <v>0.8921207999999999</v>
       </c>
       <c r="N5">
-        <v>88.80590939999999</v>
+        <v>88.58287919999999</v>
       </c>
       <c r="O5">
-        <v>17.76118188</v>
+        <v>17.71657584</v>
       </c>
       <c r="P5">
-        <v>71.04472752</v>
+        <v>70.86630335999999</v>
       </c>
       <c r="Q5">
-        <v>72.69472752</v>
+        <v>72.51630335999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1123125110670277</v>
+        <v>0.1128701276923381</v>
       </c>
       <c r="T5">
-        <v>0.7283392580610063</v>
+        <v>0.7344453886617862</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>133.7262846018162</v>
+        <v>100.2947134513622</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1099649225846446</v>
+        <v>0.1097795094342723</v>
       </c>
       <c r="C6">
-        <v>456.0662076771467</v>
+        <v>452.4915533003772</v>
       </c>
       <c r="D6">
-        <v>460.9022076771467</v>
+        <v>461.7615533003773</v>
       </c>
       <c r="E6">
-        <v>-182.264</v>
+        <v>-177.83</v>
       </c>
       <c r="F6">
-        <v>17.736</v>
+        <v>22.17</v>
       </c>
       <c r="G6">
         <v>12.9</v>
@@ -1779,28 +1779,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M6">
-        <v>0.8921207999999999</v>
+        <v>1.115151</v>
       </c>
       <c r="N6">
-        <v>88.58287919999999</v>
+        <v>88.359849</v>
       </c>
       <c r="O6">
-        <v>17.71657584</v>
+        <v>17.6719698</v>
       </c>
       <c r="P6">
-        <v>70.86630335999999</v>
+        <v>70.6878792</v>
       </c>
       <c r="Q6">
-        <v>72.51630335999999</v>
+        <v>72.3378792</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1128701276923381</v>
+        <v>0.1134394836150235</v>
       </c>
       <c r="T6">
-        <v>0.7344453886617862</v>
+        <v>0.7406800693804769</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>100.2947134513622</v>
+        <v>80.23577076108975</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1097795094342723</v>
+        <v>0.1095940962839001</v>
       </c>
       <c r="C7">
-        <v>452.4915533003772</v>
+        <v>448.9201093848975</v>
       </c>
       <c r="D7">
-        <v>461.7615533003773</v>
+        <v>462.6241093848975</v>
       </c>
       <c r="E7">
-        <v>-177.83</v>
+        <v>-173.396</v>
       </c>
       <c r="F7">
-        <v>22.17</v>
+        <v>26.604</v>
       </c>
       <c r="G7">
         <v>12.9</v>
@@ -1861,28 +1861,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M7">
-        <v>1.115151</v>
+        <v>1.3381812</v>
       </c>
       <c r="N7">
-        <v>88.359849</v>
+        <v>88.1368188</v>
       </c>
       <c r="O7">
-        <v>17.6719698</v>
+        <v>17.62736376</v>
       </c>
       <c r="P7">
-        <v>70.6878792</v>
+        <v>70.50945504000001</v>
       </c>
       <c r="Q7">
-        <v>72.3378792</v>
+        <v>72.15945504000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1134394836150235</v>
+        <v>0.1140209534935107</v>
       </c>
       <c r="T7">
-        <v>0.7406800693804769</v>
+        <v>0.7470474028804167</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>80.23577076108975</v>
+        <v>66.86314230090814</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1095940962839001</v>
+        <v>0.1094086831335278</v>
       </c>
       <c r="C8">
-        <v>448.9201093848975</v>
+        <v>445.3518939555001</v>
       </c>
       <c r="D8">
-        <v>462.6241093848975</v>
+        <v>463.4898939555002</v>
       </c>
       <c r="E8">
-        <v>-173.396</v>
+        <v>-168.962</v>
       </c>
       <c r="F8">
-        <v>26.604</v>
+        <v>31.038</v>
       </c>
       <c r="G8">
         <v>12.9</v>
@@ -1943,28 +1943,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M8">
-        <v>1.3381812</v>
+        <v>1.5612114</v>
       </c>
       <c r="N8">
-        <v>88.1368188</v>
+        <v>87.91378859999999</v>
       </c>
       <c r="O8">
-        <v>17.62736376</v>
+        <v>17.58275772</v>
       </c>
       <c r="P8">
-        <v>70.50945504000001</v>
+        <v>70.33103087999999</v>
       </c>
       <c r="Q8">
-        <v>72.15945504000001</v>
+        <v>71.98103087999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1140209534935107</v>
+        <v>0.1146149281005676</v>
       </c>
       <c r="T8">
-        <v>0.7470474028804167</v>
+        <v>0.7535516682835808</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>66.86314230090814</v>
+        <v>57.31126482934983</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1094086831335278</v>
+        <v>0.1092232699831556</v>
       </c>
       <c r="C9">
-        <v>445.3518939555001</v>
+        <v>441.7869251721618</v>
       </c>
       <c r="D9">
-        <v>463.4898939555002</v>
+        <v>464.3589251721618</v>
       </c>
       <c r="E9">
-        <v>-168.962</v>
+        <v>-164.528</v>
       </c>
       <c r="F9">
-        <v>31.038</v>
+        <v>35.472</v>
       </c>
       <c r="G9">
         <v>12.9</v>
@@ -2025,28 +2025,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M9">
-        <v>1.5612114</v>
+        <v>1.7842416</v>
       </c>
       <c r="N9">
-        <v>87.91378859999999</v>
+        <v>87.69075839999999</v>
       </c>
       <c r="O9">
-        <v>17.58275772</v>
+        <v>17.53815168</v>
       </c>
       <c r="P9">
-        <v>70.33103087999999</v>
+        <v>70.15260671999999</v>
       </c>
       <c r="Q9">
-        <v>71.98103087999999</v>
+        <v>71.80260672</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1146149281005676</v>
+        <v>0.1152218151990821</v>
       </c>
       <c r="T9">
-        <v>0.7535516682835808</v>
+        <v>0.7601973307607267</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>57.31126482934982</v>
+        <v>50.14735672568109</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1092232699831556</v>
+        <v>0.1090378568327833</v>
       </c>
       <c r="C10">
-        <v>441.7869251721618</v>
+        <v>438.2252213313123</v>
       </c>
       <c r="D10">
-        <v>464.3589251721618</v>
+        <v>465.2312213313123</v>
       </c>
       <c r="E10">
-        <v>-164.528</v>
+        <v>-160.094</v>
       </c>
       <c r="F10">
-        <v>35.472</v>
+        <v>39.906</v>
       </c>
       <c r="G10">
         <v>12.9</v>
@@ -2107,28 +2107,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M10">
-        <v>1.7842416</v>
+        <v>2.0072718</v>
       </c>
       <c r="N10">
-        <v>87.69075839999999</v>
+        <v>87.4677282</v>
       </c>
       <c r="O10">
-        <v>17.53815168</v>
+        <v>17.49354564</v>
       </c>
       <c r="P10">
-        <v>70.15260671999999</v>
+        <v>69.97418256</v>
       </c>
       <c r="Q10">
-        <v>71.80260672</v>
+        <v>71.62418256000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1152218151990821</v>
+        <v>0.115842040475586</v>
       </c>
       <c r="T10">
-        <v>0.7601973307607267</v>
+        <v>0.7669890517538539</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>50.14735672568109</v>
+        <v>44.57542820060542</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1090378568327833</v>
+        <v>0.108852443682411</v>
       </c>
       <c r="C11">
-        <v>438.2252213313123</v>
+        <v>434.6668008671199</v>
       </c>
       <c r="D11">
-        <v>465.2312213313123</v>
+        <v>466.1068008671199</v>
       </c>
       <c r="E11">
-        <v>-160.094</v>
+        <v>-155.66</v>
       </c>
       <c r="F11">
-        <v>39.906</v>
+        <v>44.34</v>
       </c>
       <c r="G11">
         <v>12.9</v>
@@ -2189,28 +2189,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M11">
-        <v>2.0072718</v>
+        <v>2.230302</v>
       </c>
       <c r="N11">
-        <v>87.4677282</v>
+        <v>87.244698</v>
       </c>
       <c r="O11">
-        <v>17.49354564</v>
+        <v>17.4489396</v>
       </c>
       <c r="P11">
-        <v>69.97418256</v>
+        <v>69.7957584</v>
       </c>
       <c r="Q11">
-        <v>71.62418256000001</v>
+        <v>71.4457584</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.115842040475586</v>
+        <v>0.1164760485360122</v>
       </c>
       <c r="T11">
-        <v>0.7669890517538539</v>
+        <v>0.7739316998801616</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.57542820060542</v>
+        <v>40.11788538054488</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.108852443682411</v>
+        <v>0.1086670305320387</v>
       </c>
       <c r="C12">
-        <v>434.6668008671197</v>
+        <v>431.1116823527888</v>
       </c>
       <c r="D12">
-        <v>466.1068008671197</v>
+        <v>466.9856823527888</v>
       </c>
       <c r="E12">
-        <v>-155.66</v>
+        <v>-151.226</v>
       </c>
       <c r="F12">
-        <v>44.34</v>
+        <v>48.774</v>
       </c>
       <c r="G12">
         <v>12.9</v>
@@ -2271,28 +2271,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M12">
-        <v>2.230302</v>
+        <v>2.4533322</v>
       </c>
       <c r="N12">
-        <v>87.244698</v>
+        <v>87.02166779999999</v>
       </c>
       <c r="O12">
-        <v>17.4489396</v>
+        <v>17.40433356</v>
       </c>
       <c r="P12">
-        <v>69.7957584</v>
+        <v>69.61733423999999</v>
       </c>
       <c r="Q12">
-        <v>71.4457584</v>
+        <v>71.26733424</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1164760485360123</v>
+        <v>0.1171243039685829</v>
       </c>
       <c r="T12">
-        <v>0.7739316998801619</v>
+        <v>0.7810303625711056</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>40.11788538054488</v>
+        <v>36.47080489140443</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1086670305320387</v>
+        <v>0.1084816173816665</v>
       </c>
       <c r="C13">
-        <v>431.1116823527888</v>
+        <v>427.5598845018731</v>
       </c>
       <c r="D13">
-        <v>466.9856823527888</v>
+        <v>467.8678845018731</v>
       </c>
       <c r="E13">
-        <v>-151.226</v>
+        <v>-146.792</v>
       </c>
       <c r="F13">
-        <v>48.774</v>
+        <v>53.208</v>
       </c>
       <c r="G13">
         <v>12.9</v>
@@ -2353,28 +2353,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M13">
-        <v>2.4533322</v>
+        <v>2.6763624</v>
       </c>
       <c r="N13">
-        <v>87.02166779999999</v>
+        <v>86.79863759999999</v>
       </c>
       <c r="O13">
-        <v>17.40433356</v>
+        <v>17.35972752</v>
       </c>
       <c r="P13">
-        <v>69.61733423999999</v>
+        <v>69.43891008</v>
       </c>
       <c r="Q13">
-        <v>71.26733424</v>
+        <v>71.08891008000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1171243039685829</v>
+        <v>0.1177872924791665</v>
       </c>
       <c r="T13">
-        <v>0.7810303625711056</v>
+        <v>0.7882903585050256</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.47080489140443</v>
+        <v>33.43157115045406</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1084816173816665</v>
+        <v>0.1082962042312942</v>
       </c>
       <c r="C14">
-        <v>427.5598845018731</v>
+        <v>424.0114261696046</v>
       </c>
       <c r="D14">
-        <v>467.8678845018731</v>
+        <v>468.7534261696046</v>
       </c>
       <c r="E14">
-        <v>-146.792</v>
+        <v>-142.358</v>
       </c>
       <c r="F14">
-        <v>53.208</v>
+        <v>57.642</v>
       </c>
       <c r="G14">
         <v>12.9</v>
@@ -2435,28 +2435,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M14">
-        <v>2.6763624</v>
+        <v>2.8993926</v>
       </c>
       <c r="N14">
-        <v>86.79863759999999</v>
+        <v>86.5756074</v>
       </c>
       <c r="O14">
-        <v>17.35972752</v>
+        <v>17.31512148</v>
       </c>
       <c r="P14">
-        <v>69.43891008</v>
+        <v>69.26048591999999</v>
       </c>
       <c r="Q14">
-        <v>71.08891008000001</v>
+        <v>70.91048592</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1177872924791665</v>
+        <v>0.1184655221049359</v>
       </c>
       <c r="T14">
-        <v>0.7882903585050256</v>
+        <v>0.7957172508971965</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.43157115045406</v>
+        <v>30.85991183118837</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1082962042312942</v>
+        <v>0.1081107910809219</v>
       </c>
       <c r="C15">
-        <v>424.0114261696046</v>
+        <v>420.4663263542366</v>
       </c>
       <c r="D15">
-        <v>468.7534261696046</v>
+        <v>469.6423263542367</v>
       </c>
       <c r="E15">
-        <v>-142.358</v>
+        <v>-137.924</v>
       </c>
       <c r="F15">
-        <v>57.642</v>
+        <v>62.076</v>
       </c>
       <c r="G15">
         <v>12.9</v>
@@ -2517,28 +2517,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M15">
-        <v>2.8993926</v>
+        <v>3.1224228</v>
       </c>
       <c r="N15">
-        <v>86.5756074</v>
+        <v>86.3525772</v>
       </c>
       <c r="O15">
-        <v>17.31512148</v>
+        <v>17.27051544</v>
       </c>
       <c r="P15">
-        <v>69.26048591999999</v>
+        <v>69.08206176</v>
       </c>
       <c r="Q15">
-        <v>70.91048592</v>
+        <v>70.73206176000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1184655221049359</v>
+        <v>0.1191595245126999</v>
       </c>
       <c r="T15">
-        <v>0.7957172508971965</v>
+        <v>0.8033168617170924</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.85991183118837</v>
+        <v>28.65563241467491</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1081107910809219</v>
+        <v>0.1079253779305497</v>
       </c>
       <c r="C16">
-        <v>420.4663263542366</v>
+        <v>416.9246041984018</v>
       </c>
       <c r="D16">
-        <v>469.6423263542367</v>
+        <v>470.5346041984018</v>
       </c>
       <c r="E16">
-        <v>-137.924</v>
+        <v>-133.49</v>
       </c>
       <c r="F16">
-        <v>62.076</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="G16">
         <v>12.9</v>
@@ -2599,28 +2599,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M16">
-        <v>3.1224228</v>
+        <v>3.345453</v>
       </c>
       <c r="N16">
-        <v>86.3525772</v>
+        <v>86.12954699999999</v>
       </c>
       <c r="O16">
-        <v>17.27051544</v>
+        <v>17.2259094</v>
       </c>
       <c r="P16">
-        <v>69.08206176</v>
+        <v>68.9036376</v>
       </c>
       <c r="Q16">
-        <v>70.73206176000001</v>
+        <v>70.5536376</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1191595245126999</v>
+        <v>0.119869856388882</v>
       </c>
       <c r="T16">
-        <v>0.8033168617170924</v>
+        <v>0.8110952869092211</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.65563241467491</v>
+        <v>26.74525692036325</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1079253779305497</v>
+        <v>0.1077399647801774</v>
       </c>
       <c r="C17">
-        <v>416.9246041984018</v>
+        <v>413.3862789904873</v>
       </c>
       <c r="D17">
-        <v>470.5346041984018</v>
+        <v>471.4302789904874</v>
       </c>
       <c r="E17">
-        <v>-133.49</v>
+        <v>-129.056</v>
       </c>
       <c r="F17">
-        <v>66.50999999999999</v>
+        <v>70.944</v>
       </c>
       <c r="G17">
         <v>12.9</v>
@@ -2681,28 +2681,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M17">
-        <v>3.345453</v>
+        <v>3.5684832</v>
       </c>
       <c r="N17">
-        <v>86.12954699999999</v>
+        <v>85.90651679999999</v>
       </c>
       <c r="O17">
-        <v>17.2259094</v>
+        <v>17.18130336</v>
       </c>
       <c r="P17">
-        <v>68.9036376</v>
+        <v>68.72521343999999</v>
       </c>
       <c r="Q17">
-        <v>70.5536376</v>
+        <v>70.37521344</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.119869856388882</v>
+        <v>0.1205971009287826</v>
       </c>
       <c r="T17">
-        <v>0.8110952869092211</v>
+        <v>0.8190589127011624</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.74525692036325</v>
+        <v>25.07367836284055</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1077399647801774</v>
+        <v>0.1075545516298051</v>
       </c>
       <c r="C18">
-        <v>413.3862789904873</v>
+        <v>409.8513701660236</v>
       </c>
       <c r="D18">
-        <v>471.4302789904874</v>
+        <v>472.3293701660236</v>
       </c>
       <c r="E18">
-        <v>-129.056</v>
+        <v>-124.622</v>
       </c>
       <c r="F18">
-        <v>70.944</v>
+        <v>75.378</v>
       </c>
       <c r="G18">
         <v>12.9</v>
@@ -2763,28 +2763,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M18">
-        <v>3.5684832</v>
+        <v>3.7915134</v>
       </c>
       <c r="N18">
-        <v>85.90651679999999</v>
+        <v>85.68348659999999</v>
       </c>
       <c r="O18">
-        <v>17.18130336</v>
+        <v>17.13669732</v>
       </c>
       <c r="P18">
-        <v>68.72521343999999</v>
+        <v>68.54678928</v>
       </c>
       <c r="Q18">
-        <v>70.37521344</v>
+        <v>70.19678928</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1205971009287826</v>
+        <v>0.1213418694335002</v>
       </c>
       <c r="T18">
-        <v>0.8190589127011624</v>
+        <v>0.8272144330904998</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.07367836284055</v>
+        <v>23.59875610620287</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1075545516298051</v>
+        <v>0.1073691384794329</v>
       </c>
       <c r="C19">
-        <v>409.8513701660236</v>
+        <v>406.3198973090913</v>
       </c>
       <c r="D19">
-        <v>472.3293701660236</v>
+        <v>473.2318973090913</v>
       </c>
       <c r="E19">
-        <v>-124.622</v>
+        <v>-120.188</v>
       </c>
       <c r="F19">
-        <v>75.378</v>
+        <v>79.81200000000001</v>
       </c>
       <c r="G19">
         <v>12.9</v>
@@ -2845,28 +2845,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M19">
-        <v>3.7915134</v>
+        <v>4.014543600000001</v>
       </c>
       <c r="N19">
-        <v>85.68348659999999</v>
+        <v>85.4604564</v>
       </c>
       <c r="O19">
-        <v>17.13669732</v>
+        <v>17.09209128</v>
       </c>
       <c r="P19">
-        <v>68.54678928</v>
+        <v>68.36836511999999</v>
       </c>
       <c r="Q19">
-        <v>70.19678928</v>
+        <v>70.01836512</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1213418694335002</v>
+        <v>0.1221048030236986</v>
       </c>
       <c r="T19">
-        <v>0.8272144330904998</v>
+        <v>0.8355688686112848</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.59875610620287</v>
+        <v>22.28771410030271</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1073691384794329</v>
+        <v>0.1071837253290606</v>
       </c>
       <c r="C20">
-        <v>406.3198973090913</v>
+        <v>402.7918801537426</v>
       </c>
       <c r="D20">
-        <v>473.2318973090913</v>
+        <v>474.1378801537426</v>
       </c>
       <c r="E20">
-        <v>-120.188</v>
+        <v>-115.754</v>
       </c>
       <c r="F20">
-        <v>79.812</v>
+        <v>84.246</v>
       </c>
       <c r="G20">
         <v>12.9</v>
@@ -2927,28 +2927,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M20">
-        <v>4.0145436</v>
+        <v>4.2375738</v>
       </c>
       <c r="N20">
-        <v>85.4604564</v>
+        <v>85.23742619999999</v>
       </c>
       <c r="O20">
-        <v>17.09209128</v>
+        <v>17.04748524</v>
       </c>
       <c r="P20">
-        <v>68.36836511999999</v>
+        <v>68.18994095999999</v>
       </c>
       <c r="Q20">
-        <v>70.01836512</v>
+        <v>69.83994095999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1221048030236986</v>
+        <v>0.1228865744803218</v>
       </c>
       <c r="T20">
-        <v>0.8355688686112845</v>
+        <v>0.8441295864906073</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.28771410030271</v>
+        <v>21.11467651607625</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1071837253290606</v>
+        <v>0.1069983121786884</v>
       </c>
       <c r="C21">
-        <v>402.7918801537426</v>
+        <v>399.2673385854395</v>
       </c>
       <c r="D21">
-        <v>474.1378801537426</v>
+        <v>475.0473385854395</v>
       </c>
       <c r="E21">
-        <v>-115.754</v>
+        <v>-111.32</v>
       </c>
       <c r="F21">
-        <v>84.246</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="G21">
         <v>12.9</v>
@@ -3009,28 +3009,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M21">
-        <v>4.2375738</v>
+        <v>4.460604</v>
       </c>
       <c r="N21">
-        <v>85.23742619999999</v>
+        <v>85.01439599999999</v>
       </c>
       <c r="O21">
-        <v>17.04748524</v>
+        <v>17.0028792</v>
       </c>
       <c r="P21">
-        <v>68.18994095999999</v>
+        <v>68.0115168</v>
       </c>
       <c r="Q21">
-        <v>69.83994095999999</v>
+        <v>69.6615168</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1228865744803218</v>
+        <v>0.1236878902233604</v>
       </c>
       <c r="T21">
-        <v>0.8441295864906073</v>
+        <v>0.8529043223169129</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.11467651607625</v>
+        <v>20.05894269027243</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1069983121786884</v>
+        <v>0.1068128990283161</v>
       </c>
       <c r="C22">
-        <v>399.2673385854395</v>
+        <v>395.746292642509</v>
       </c>
       <c r="D22">
-        <v>475.0473385854395</v>
+        <v>475.9602926425091</v>
       </c>
       <c r="E22">
-        <v>-111.32</v>
+        <v>-106.886</v>
       </c>
       <c r="F22">
-        <v>88.68000000000001</v>
+        <v>93.114</v>
       </c>
       <c r="G22">
         <v>12.9</v>
@@ -3091,28 +3091,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M22">
-        <v>4.460604</v>
+        <v>4.6836342</v>
       </c>
       <c r="N22">
-        <v>85.01439599999999</v>
+        <v>84.79136579999999</v>
       </c>
       <c r="O22">
-        <v>17.0028792</v>
+        <v>16.95827316</v>
       </c>
       <c r="P22">
-        <v>68.0115168</v>
+        <v>67.83309263999999</v>
       </c>
       <c r="Q22">
-        <v>69.6615168</v>
+        <v>69.48309264</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1236878902233604</v>
+        <v>0.1245094924409064</v>
       </c>
       <c r="T22">
-        <v>0.8529043223169129</v>
+        <v>0.8619012033540112</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.05894269027243</v>
+        <v>19.10375494311661</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1068128990283161</v>
+        <v>0.1066274858779438</v>
       </c>
       <c r="C23">
-        <v>395.7462926425091</v>
+        <v>392.2287625176145</v>
       </c>
       <c r="D23">
-        <v>475.9602926425091</v>
+        <v>476.8767625176146</v>
       </c>
       <c r="E23">
-        <v>-106.886</v>
+        <v>-102.452</v>
       </c>
       <c r="F23">
-        <v>93.11399999999999</v>
+        <v>97.548</v>
       </c>
       <c r="G23">
         <v>12.9</v>
@@ -3173,28 +3173,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M23">
-        <v>4.683634199999999</v>
+        <v>4.906664399999999</v>
       </c>
       <c r="N23">
-        <v>84.79136579999999</v>
+        <v>84.5683356</v>
       </c>
       <c r="O23">
-        <v>16.95827316</v>
+        <v>16.91366712</v>
       </c>
       <c r="P23">
-        <v>67.83309263999999</v>
+        <v>67.65466848</v>
       </c>
       <c r="Q23">
-        <v>69.48309264</v>
+        <v>69.30466848</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1245094924409064</v>
+        <v>0.1253521613819792</v>
       </c>
       <c r="T23">
-        <v>0.8619012033540112</v>
+        <v>0.871128773648471</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.10375494311661</v>
+        <v>18.23540244570222</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1066274858779438</v>
+        <v>0.1064420727275716</v>
       </c>
       <c r="C24">
-        <v>392.2287625176145</v>
+        <v>388.7147685592448</v>
       </c>
       <c r="D24">
-        <v>476.8767625176146</v>
+        <v>477.7967685592449</v>
       </c>
       <c r="E24">
-        <v>-102.452</v>
+        <v>-98.018</v>
       </c>
       <c r="F24">
-        <v>97.548</v>
+        <v>101.982</v>
       </c>
       <c r="G24">
         <v>12.9</v>
@@ -3255,28 +3255,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M24">
-        <v>4.906664399999999</v>
+        <v>5.1296946</v>
       </c>
       <c r="N24">
-        <v>84.5683356</v>
+        <v>84.3453054</v>
       </c>
       <c r="O24">
-        <v>16.91366712</v>
+        <v>16.86906108</v>
       </c>
       <c r="P24">
-        <v>67.65466848</v>
+        <v>67.47624432000001</v>
       </c>
       <c r="Q24">
-        <v>69.30466848</v>
+        <v>69.12624432000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1253521613819792</v>
+        <v>0.126216717828015</v>
       </c>
       <c r="T24">
-        <v>0.871128773648471</v>
+        <v>0.8805960210934362</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.23540244570222</v>
+        <v>17.44255886110647</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1064420727275716</v>
+        <v>0.1062566595771993</v>
       </c>
       <c r="C25">
-        <v>388.7147685592448</v>
+        <v>385.2043312732205</v>
       </c>
       <c r="D25">
-        <v>477.7967685592449</v>
+        <v>478.7203312732205</v>
       </c>
       <c r="E25">
-        <v>-98.018</v>
+        <v>-93.584</v>
       </c>
       <c r="F25">
-        <v>101.982</v>
+        <v>106.416</v>
       </c>
       <c r="G25">
         <v>12.9</v>
@@ -3337,28 +3337,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M25">
-        <v>5.1296946</v>
+        <v>5.3527248</v>
       </c>
       <c r="N25">
-        <v>84.3453054</v>
+        <v>84.12227519999999</v>
       </c>
       <c r="O25">
-        <v>16.86906108</v>
+        <v>16.82445504</v>
       </c>
       <c r="P25">
-        <v>67.47624432000001</v>
+        <v>67.29782015999999</v>
       </c>
       <c r="Q25">
-        <v>69.12624432000001</v>
+        <v>68.94782015999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.126216717828015</v>
+        <v>0.1271040257594727</v>
       </c>
       <c r="T25">
-        <v>0.8805960210934362</v>
+        <v>0.8903124066290583</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.44255886110647</v>
+        <v>16.71578557522703</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1062566595771993</v>
+        <v>0.106071246426827</v>
       </c>
       <c r="C26">
-        <v>385.2043312732206</v>
+        <v>381.6974713242165</v>
       </c>
       <c r="D26">
-        <v>478.7203312732206</v>
+        <v>479.6474713242165</v>
       </c>
       <c r="E26">
-        <v>-93.584</v>
+        <v>-89.15000000000001</v>
       </c>
       <c r="F26">
-        <v>106.416</v>
+        <v>110.85</v>
       </c>
       <c r="G26">
         <v>12.9</v>
@@ -3419,28 +3419,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M26">
-        <v>5.3527248</v>
+        <v>5.575754999999999</v>
       </c>
       <c r="N26">
-        <v>84.12227519999999</v>
+        <v>83.89924499999999</v>
       </c>
       <c r="O26">
-        <v>16.82445504</v>
+        <v>16.779849</v>
       </c>
       <c r="P26">
-        <v>67.29782015999999</v>
+        <v>67.11939599999999</v>
       </c>
       <c r="Q26">
-        <v>68.94782015999999</v>
+        <v>68.769396</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1271040257594727</v>
+        <v>0.1280149952357693</v>
       </c>
       <c r="T26">
-        <v>0.8903124066290582</v>
+        <v>0.9002878957789636</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.71578557522703</v>
+        <v>16.04715415221795</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.106071246426827</v>
+        <v>0.1058858332764547</v>
       </c>
       <c r="C27">
-        <v>381.6974713242165</v>
+        <v>378.1942095373042</v>
       </c>
       <c r="D27">
-        <v>479.6474713242165</v>
+        <v>480.5782095373042</v>
       </c>
       <c r="E27">
-        <v>-89.15000000000001</v>
+        <v>-84.71600000000001</v>
       </c>
       <c r="F27">
-        <v>110.85</v>
+        <v>115.284</v>
       </c>
       <c r="G27">
         <v>12.9</v>
@@ -3501,28 +3501,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M27">
-        <v>5.575754999999999</v>
+        <v>5.798785199999999</v>
       </c>
       <c r="N27">
-        <v>83.89924499999999</v>
+        <v>83.6762148</v>
       </c>
       <c r="O27">
-        <v>16.779849</v>
+        <v>16.73524296</v>
       </c>
       <c r="P27">
-        <v>67.11939599999999</v>
+        <v>66.94097184</v>
       </c>
       <c r="Q27">
-        <v>68.769396</v>
+        <v>68.59097184000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1280149952357693</v>
+        <v>0.1289505855087226</v>
       </c>
       <c r="T27">
-        <v>0.9002878957789636</v>
+        <v>0.9105329927437313</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.04715415221795</v>
+        <v>15.42995591559419</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1058858332764547</v>
+        <v>0.1057004201260825</v>
       </c>
       <c r="C28">
-        <v>378.1942095373042</v>
+        <v>374.6945668995102</v>
       </c>
       <c r="D28">
-        <v>480.5782095373042</v>
+        <v>481.5125668995102</v>
       </c>
       <c r="E28">
-        <v>-84.71600000000001</v>
+        <v>-80.282</v>
       </c>
       <c r="F28">
-        <v>115.284</v>
+        <v>119.718</v>
       </c>
       <c r="G28">
         <v>12.9</v>
@@ -3583,28 +3583,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M28">
-        <v>5.798785199999999</v>
+        <v>6.021815399999999</v>
       </c>
       <c r="N28">
-        <v>83.6762148</v>
+        <v>83.4531846</v>
       </c>
       <c r="O28">
-        <v>16.73524296</v>
+        <v>16.69063692</v>
       </c>
       <c r="P28">
-        <v>66.94097184</v>
+        <v>66.76254768</v>
       </c>
       <c r="Q28">
-        <v>68.59097184000001</v>
+        <v>68.41254768</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1289505855087226</v>
+        <v>0.1299118083918938</v>
       </c>
       <c r="T28">
-        <v>0.9105329927437313</v>
+        <v>0.921058777296575</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.42995591559419</v>
+        <v>14.85847606686847</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1057004201260825</v>
+        <v>0.1055150069757102</v>
       </c>
       <c r="C29">
-        <v>374.6945668995102</v>
+        <v>371.1985645613944</v>
       </c>
       <c r="D29">
-        <v>481.5125668995102</v>
+        <v>482.4505645613944</v>
       </c>
       <c r="E29">
-        <v>-80.282</v>
+        <v>-75.848</v>
       </c>
       <c r="F29">
-        <v>119.718</v>
+        <v>124.152</v>
       </c>
       <c r="G29">
         <v>12.9</v>
@@ -3665,28 +3665,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M29">
-        <v>6.021815399999999</v>
+        <v>6.2448456</v>
       </c>
       <c r="N29">
-        <v>83.4531846</v>
+        <v>83.23015439999999</v>
       </c>
       <c r="O29">
-        <v>16.69063692</v>
+        <v>16.64603088</v>
       </c>
       <c r="P29">
-        <v>66.76254768</v>
+        <v>66.58412351999999</v>
       </c>
       <c r="Q29">
-        <v>68.41254768</v>
+        <v>68.23412352</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1299118083918938</v>
+        <v>0.1308997319107086</v>
       </c>
       <c r="T29">
-        <v>0.921058777296575</v>
+        <v>0.9318769447536641</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.85847606686847</v>
+        <v>14.32781620733745</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1055150069757102</v>
+        <v>0.1053295938253379</v>
       </c>
       <c r="C30">
-        <v>371.1985645613944</v>
+        <v>367.7062238386448</v>
       </c>
       <c r="D30">
-        <v>482.4505645613944</v>
+        <v>483.3922238386448</v>
       </c>
       <c r="E30">
-        <v>-75.848</v>
+        <v>-71.41399999999999</v>
       </c>
       <c r="F30">
-        <v>124.152</v>
+        <v>128.586</v>
       </c>
       <c r="G30">
         <v>12.9</v>
@@ -3747,28 +3747,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M30">
-        <v>6.2448456</v>
+        <v>6.467875800000001</v>
       </c>
       <c r="N30">
-        <v>83.23015439999999</v>
+        <v>83.00712419999999</v>
       </c>
       <c r="O30">
-        <v>16.64603088</v>
+        <v>16.60142484</v>
       </c>
       <c r="P30">
-        <v>66.58412351999999</v>
+        <v>66.40569936</v>
       </c>
       <c r="Q30">
-        <v>68.23412352</v>
+        <v>68.05569936000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1308997319107086</v>
+        <v>0.1319154842610394</v>
       </c>
       <c r="T30">
-        <v>0.9318769447536641</v>
+        <v>0.9429998493222206</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.32781620733745</v>
+        <v>13.83375357949823</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1053295938253379</v>
+        <v>0.1051441806749657</v>
       </c>
       <c r="C31">
-        <v>367.7062238386449</v>
+        <v>364.2175662136935</v>
       </c>
       <c r="D31">
-        <v>483.3922238386448</v>
+        <v>484.3375662136935</v>
       </c>
       <c r="E31">
-        <v>-71.41400000000002</v>
+        <v>-66.98000000000002</v>
       </c>
       <c r="F31">
-        <v>128.586</v>
+        <v>133.02</v>
       </c>
       <c r="G31">
         <v>12.9</v>
@@ -3829,28 +3829,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M31">
-        <v>6.467875799999999</v>
+        <v>6.690905999999999</v>
       </c>
       <c r="N31">
-        <v>83.00712419999999</v>
+        <v>82.784094</v>
       </c>
       <c r="O31">
-        <v>16.60142484</v>
+        <v>16.5568188</v>
       </c>
       <c r="P31">
-        <v>66.40569936</v>
+        <v>66.22727519999999</v>
       </c>
       <c r="Q31">
-        <v>68.05569936000001</v>
+        <v>67.8772752</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1319154842610394</v>
+        <v>0.1329602581070938</v>
       </c>
       <c r="T31">
-        <v>0.9429998493222206</v>
+        <v>0.9544405511641645</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.83375357949823</v>
+        <v>13.37262846018163</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1051441806749657</v>
+        <v>0.1049587675245934</v>
       </c>
       <c r="C32">
-        <v>364.2175662136935</v>
+        <v>360.7326133373492</v>
       </c>
       <c r="D32">
-        <v>484.3375662136935</v>
+        <v>485.2866133373492</v>
       </c>
       <c r="E32">
-        <v>-66.98000000000002</v>
+        <v>-62.54600000000002</v>
       </c>
       <c r="F32">
-        <v>133.02</v>
+        <v>137.454</v>
       </c>
       <c r="G32">
         <v>12.9</v>
@@ -3911,28 +3911,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M32">
-        <v>6.690905999999999</v>
+        <v>6.913936199999998</v>
       </c>
       <c r="N32">
-        <v>82.784094</v>
+        <v>82.5610638</v>
       </c>
       <c r="O32">
-        <v>16.5568188</v>
+        <v>16.51221276</v>
       </c>
       <c r="P32">
-        <v>66.22727519999999</v>
+        <v>66.04885104</v>
       </c>
       <c r="Q32">
-        <v>67.8772752</v>
+        <v>67.69885104000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1329602581070938</v>
+        <v>0.1340353152530339</v>
       </c>
       <c r="T32">
-        <v>0.9544405511641645</v>
+        <v>0.9662128675522516</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.37262846018163</v>
+        <v>12.94125334856287</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1049587675245934</v>
+        <v>0.1051573543742211</v>
       </c>
       <c r="C33">
-        <v>360.7326133373492</v>
+        <v>355.2822771490009</v>
       </c>
       <c r="D33">
-        <v>485.2866133373492</v>
+        <v>484.2702771490009</v>
       </c>
       <c r="E33">
-        <v>-62.54600000000002</v>
+        <v>-58.11199999999999</v>
       </c>
       <c r="F33">
-        <v>137.454</v>
+        <v>141.888</v>
       </c>
       <c r="G33">
         <v>12.9</v>
@@ -3993,45 +3993,45 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M33">
-        <v>6.913936199999998</v>
+        <v>7.3497984</v>
       </c>
       <c r="N33">
-        <v>82.5610638</v>
+        <v>82.1252016</v>
       </c>
       <c r="O33">
-        <v>16.51221276</v>
+        <v>16.42504032</v>
       </c>
       <c r="P33">
-        <v>66.04885104</v>
+        <v>65.70016128</v>
       </c>
       <c r="Q33">
-        <v>67.69885104000001</v>
+        <v>67.35016128000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1340353152530339</v>
+        <v>0.1351419917267958</v>
       </c>
       <c r="T33">
-        <v>0.9662128675522516</v>
+        <v>0.9783314285399883</v>
       </c>
       <c r="U33">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>12.94125334856287</v>
+        <v>12.17380329778841</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1051573543742211</v>
+        <v>0.1049839412238489</v>
       </c>
       <c r="C34">
-        <v>355.2822771490009</v>
+        <v>351.7355422657276</v>
       </c>
       <c r="D34">
-        <v>484.2702771490009</v>
+        <v>485.1575422657276</v>
       </c>
       <c r="E34">
-        <v>-58.11199999999999</v>
+        <v>-53.678</v>
       </c>
       <c r="F34">
-        <v>141.888</v>
+        <v>146.322</v>
       </c>
       <c r="G34">
         <v>12.9</v>
@@ -4075,28 +4075,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M34">
-        <v>7.3497984</v>
+        <v>7.5794796</v>
       </c>
       <c r="N34">
-        <v>82.1252016</v>
+        <v>81.8955204</v>
       </c>
       <c r="O34">
-        <v>16.42504032</v>
+        <v>16.37910408</v>
       </c>
       <c r="P34">
-        <v>65.70016128</v>
+        <v>65.51641631999999</v>
       </c>
       <c r="Q34">
-        <v>67.35016128000001</v>
+        <v>67.16641632</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1351419917267958</v>
+        <v>0.1362817033191774</v>
       </c>
       <c r="T34">
-        <v>0.9783314285399883</v>
+        <v>0.9908117376169113</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.17380329778841</v>
+        <v>11.8049001675524</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1049839412238489</v>
+        <v>0.1048105280734766</v>
       </c>
       <c r="C35">
-        <v>351.7355422657276</v>
+        <v>348.1920645899594</v>
       </c>
       <c r="D35">
-        <v>485.1575422657276</v>
+        <v>486.0480645899594</v>
       </c>
       <c r="E35">
-        <v>-53.678</v>
+        <v>-49.244</v>
       </c>
       <c r="F35">
-        <v>146.322</v>
+        <v>150.756</v>
       </c>
       <c r="G35">
         <v>12.9</v>
@@ -4157,28 +4157,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M35">
-        <v>7.5794796</v>
+        <v>7.8091608</v>
       </c>
       <c r="N35">
-        <v>81.8955204</v>
+        <v>81.66583919999999</v>
       </c>
       <c r="O35">
-        <v>16.37910408</v>
+        <v>16.33316784</v>
       </c>
       <c r="P35">
-        <v>65.51641631999999</v>
+        <v>65.33267135999999</v>
       </c>
       <c r="Q35">
-        <v>67.16641632</v>
+        <v>66.98267136</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1362817033191774</v>
+        <v>0.1374559516264797</v>
       </c>
       <c r="T35">
-        <v>0.9908117376169113</v>
+        <v>1.003670237877983</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.8049001675524</v>
+        <v>11.45769722144792</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1048105280734766</v>
+        <v>0.1046371149231043</v>
       </c>
       <c r="C36">
-        <v>348.1920645899594</v>
+        <v>344.651862090808</v>
       </c>
       <c r="D36">
-        <v>486.0480645899594</v>
+        <v>486.9418620908081</v>
       </c>
       <c r="E36">
-        <v>-49.244</v>
+        <v>-44.81</v>
       </c>
       <c r="F36">
-        <v>150.756</v>
+        <v>155.19</v>
       </c>
       <c r="G36">
         <v>12.9</v>
@@ -4239,28 +4239,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M36">
-        <v>7.8091608</v>
+        <v>8.038841999999999</v>
       </c>
       <c r="N36">
-        <v>81.66583919999999</v>
+        <v>81.43615799999999</v>
       </c>
       <c r="O36">
-        <v>16.33316784</v>
+        <v>16.2872316</v>
       </c>
       <c r="P36">
-        <v>65.33267135999999</v>
+        <v>65.14892639999999</v>
       </c>
       <c r="Q36">
-        <v>66.98267136</v>
+        <v>66.7989264</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1374559516264797</v>
+        <v>0.1386663306509297</v>
       </c>
       <c r="T36">
-        <v>1.003670237877983</v>
+        <v>1.016924384300935</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.45769722144792</v>
+        <v>11.13033444369226</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1046371149231043</v>
+        <v>0.1044637017727321</v>
       </c>
       <c r="C37">
-        <v>344.651862090808</v>
+        <v>341.114952869802</v>
       </c>
       <c r="D37">
-        <v>486.9418620908081</v>
+        <v>487.8389528698021</v>
       </c>
       <c r="E37">
-        <v>-44.81</v>
+        <v>-40.37599999999998</v>
       </c>
       <c r="F37">
-        <v>155.19</v>
+        <v>159.624</v>
       </c>
       <c r="G37">
         <v>12.9</v>
@@ -4321,28 +4321,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M37">
-        <v>8.038841999999999</v>
+        <v>8.268523200000001</v>
       </c>
       <c r="N37">
-        <v>81.43615799999999</v>
+        <v>81.20647679999999</v>
       </c>
       <c r="O37">
-        <v>16.2872316</v>
+        <v>16.24129536</v>
       </c>
       <c r="P37">
-        <v>65.14892639999999</v>
+        <v>64.96518143999999</v>
       </c>
       <c r="Q37">
-        <v>66.7989264</v>
+        <v>66.61518144</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1386663306509297</v>
+        <v>0.1399145340198939</v>
       </c>
       <c r="T37">
-        <v>1.016924384300935</v>
+        <v>1.030592722799603</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.13033444369226</v>
+        <v>10.82115848692303</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1044637017727321</v>
+        <v>0.1042902886223598</v>
       </c>
       <c r="C38">
-        <v>341.1149528698021</v>
+        <v>337.5813551621103</v>
       </c>
       <c r="D38">
-        <v>487.8389528698021</v>
+        <v>488.7393551621103</v>
       </c>
       <c r="E38">
-        <v>-40.376</v>
+        <v>-35.94200000000001</v>
       </c>
       <c r="F38">
-        <v>159.624</v>
+        <v>164.058</v>
       </c>
       <c r="G38">
         <v>12.9</v>
@@ -4403,28 +4403,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M38">
-        <v>8.268523199999999</v>
+        <v>8.498204399999999</v>
       </c>
       <c r="N38">
-        <v>81.20647679999999</v>
+        <v>80.9767956</v>
       </c>
       <c r="O38">
-        <v>16.24129536</v>
+        <v>16.19535912</v>
       </c>
       <c r="P38">
-        <v>64.96518143999999</v>
+        <v>64.78143648</v>
       </c>
       <c r="Q38">
-        <v>66.61518144</v>
+        <v>66.43143648</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1399145340198938</v>
+        <v>0.1412023628926346</v>
       </c>
       <c r="T38">
-        <v>1.030592722799603</v>
+        <v>1.044694976806166</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.82115848692303</v>
+        <v>10.52869474403322</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1042902886223598</v>
+        <v>0.1041168754719875</v>
       </c>
       <c r="C39">
-        <v>337.5813551621103</v>
+        <v>334.0510873377768</v>
       </c>
       <c r="D39">
-        <v>488.7393551621103</v>
+        <v>489.6430873377768</v>
       </c>
       <c r="E39">
-        <v>-35.94200000000001</v>
+        <v>-31.50800000000001</v>
       </c>
       <c r="F39">
-        <v>164.058</v>
+        <v>168.492</v>
       </c>
       <c r="G39">
         <v>12.9</v>
@@ -4485,28 +4485,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M39">
-        <v>8.498204399999999</v>
+        <v>8.727885599999999</v>
       </c>
       <c r="N39">
-        <v>80.9767956</v>
+        <v>80.7471144</v>
       </c>
       <c r="O39">
-        <v>16.19535912</v>
+        <v>16.14942288</v>
       </c>
       <c r="P39">
-        <v>64.78143648</v>
+        <v>64.59769152</v>
       </c>
       <c r="Q39">
-        <v>66.43143648</v>
+        <v>66.24769152</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1412023628926346</v>
+        <v>0.1425317346322379</v>
       </c>
       <c r="T39">
-        <v>1.044694976806166</v>
+        <v>1.059252142232295</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.52869474403322</v>
+        <v>10.25162382971656</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1041168754719875</v>
+        <v>0.1039434623216153</v>
       </c>
       <c r="C40">
-        <v>334.0510873377768</v>
+        <v>330.5241679029697</v>
       </c>
       <c r="D40">
-        <v>489.6430873377768</v>
+        <v>490.5501679029697</v>
       </c>
       <c r="E40">
-        <v>-31.50800000000001</v>
+        <v>-27.07400000000001</v>
       </c>
       <c r="F40">
-        <v>168.492</v>
+        <v>172.926</v>
       </c>
       <c r="G40">
         <v>12.9</v>
@@ -4567,28 +4567,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M40">
-        <v>8.727885599999999</v>
+        <v>8.957566799999999</v>
       </c>
       <c r="N40">
-        <v>80.7471144</v>
+        <v>80.5174332</v>
       </c>
       <c r="O40">
-        <v>16.14942288</v>
+        <v>16.10348664</v>
       </c>
       <c r="P40">
-        <v>64.59769152</v>
+        <v>64.41394656</v>
       </c>
       <c r="Q40">
-        <v>66.24769152</v>
+        <v>66.06394656000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1425317346322379</v>
+        <v>0.1439046923305168</v>
       </c>
       <c r="T40">
-        <v>1.059252142232295</v>
+        <v>1.074286591770756</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.25162382971656</v>
+        <v>9.988761680236648</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1039434623216153</v>
+        <v>0.104314049171243</v>
       </c>
       <c r="C41">
-        <v>330.5241679029697</v>
+        <v>324.1557882898526</v>
       </c>
       <c r="D41">
-        <v>490.5501679029697</v>
+        <v>488.6157882898526</v>
       </c>
       <c r="E41">
-        <v>-27.07400000000001</v>
+        <v>-22.63999999999999</v>
       </c>
       <c r="F41">
-        <v>172.926</v>
+        <v>177.36</v>
       </c>
       <c r="G41">
         <v>12.9</v>
@@ -4649,45 +4649,45 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M41">
-        <v>8.957566799999999</v>
+        <v>9.488760000000001</v>
       </c>
       <c r="N41">
-        <v>80.5174332</v>
+        <v>79.98624</v>
       </c>
       <c r="O41">
-        <v>16.10348664</v>
+        <v>15.997248</v>
       </c>
       <c r="P41">
-        <v>64.41394656</v>
+        <v>63.988992</v>
       </c>
       <c r="Q41">
-        <v>66.06394656000001</v>
+        <v>65.638992</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1439046923305168</v>
+        <v>0.145323415285405</v>
       </c>
       <c r="T41">
-        <v>1.074286591770756</v>
+        <v>1.089822189627166</v>
       </c>
       <c r="U41">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.988761680236648</v>
+        <v>9.429577731969191</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.104314049171243</v>
+        <v>0.1041542360208707</v>
       </c>
       <c r="C42">
-        <v>324.1557882898526</v>
+        <v>320.5541027419184</v>
       </c>
       <c r="D42">
-        <v>488.6157882898526</v>
+        <v>489.4481027419185</v>
       </c>
       <c r="E42">
-        <v>-22.63999999999999</v>
+        <v>-18.20599999999999</v>
       </c>
       <c r="F42">
-        <v>177.36</v>
+        <v>181.794</v>
       </c>
       <c r="G42">
         <v>12.9</v>
@@ -4731,28 +4731,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M42">
-        <v>9.488760000000001</v>
+        <v>9.725979000000001</v>
       </c>
       <c r="N42">
-        <v>79.98624</v>
+        <v>79.749021</v>
       </c>
       <c r="O42">
-        <v>15.997248</v>
+        <v>15.9498042</v>
       </c>
       <c r="P42">
-        <v>63.988992</v>
+        <v>63.7992168</v>
       </c>
       <c r="Q42">
-        <v>65.638992</v>
+        <v>65.4492168</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.145323415285405</v>
+        <v>0.1467902305438487</v>
       </c>
       <c r="T42">
-        <v>1.089822189627166</v>
+        <v>1.105884417919387</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.429577731969191</v>
+        <v>9.199588031189457</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1041542360208707</v>
+        <v>0.1039944228704985</v>
       </c>
       <c r="C43">
-        <v>320.5541027419184</v>
+        <v>316.9552575827402</v>
       </c>
       <c r="D43">
-        <v>489.4481027419185</v>
+        <v>490.2832575827402</v>
       </c>
       <c r="E43">
-        <v>-18.20599999999999</v>
+        <v>-13.77199999999999</v>
       </c>
       <c r="F43">
-        <v>181.794</v>
+        <v>186.228</v>
       </c>
       <c r="G43">
         <v>12.9</v>
@@ -4813,28 +4813,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M43">
-        <v>9.725979000000001</v>
+        <v>9.963198</v>
       </c>
       <c r="N43">
-        <v>79.749021</v>
+        <v>79.51180199999999</v>
       </c>
       <c r="O43">
-        <v>15.9498042</v>
+        <v>15.9023604</v>
       </c>
       <c r="P43">
-        <v>63.7992168</v>
+        <v>63.60944159999999</v>
       </c>
       <c r="Q43">
-        <v>65.4492168</v>
+        <v>65.25944159999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1467902305438487</v>
+        <v>0.1483076256387905</v>
       </c>
       <c r="T43">
-        <v>1.105884417919387</v>
+        <v>1.122500516152719</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.199588031189457</v>
+        <v>8.980550220923039</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1039944228704985</v>
+        <v>0.1038346097201262</v>
       </c>
       <c r="C44">
-        <v>316.9552575827402</v>
+        <v>313.3592673770015</v>
       </c>
       <c r="D44">
-        <v>490.2832575827402</v>
+        <v>491.1212673770015</v>
       </c>
       <c r="E44">
-        <v>-13.77200000000002</v>
+        <v>-9.338000000000022</v>
       </c>
       <c r="F44">
-        <v>186.228</v>
+        <v>190.662</v>
       </c>
       <c r="G44">
         <v>12.9</v>
@@ -4895,28 +4895,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M44">
-        <v>9.963197999999998</v>
+        <v>10.200417</v>
       </c>
       <c r="N44">
-        <v>79.51180199999999</v>
+        <v>79.27458299999999</v>
       </c>
       <c r="O44">
-        <v>15.9023604</v>
+        <v>15.8549166</v>
       </c>
       <c r="P44">
-        <v>63.60944159999999</v>
+        <v>63.4196664</v>
       </c>
       <c r="Q44">
-        <v>65.25944159999999</v>
+        <v>65.0696664</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1483076256387904</v>
+        <v>0.1498782626668881</v>
       </c>
       <c r="T44">
-        <v>1.122500516152719</v>
+        <v>1.139699635376694</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.980550220923041</v>
+        <v>8.771700215785296</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1038346097201262</v>
+        <v>0.1036747965697539</v>
       </c>
       <c r="C45">
-        <v>313.3592673770015</v>
+        <v>309.7661467891351</v>
       </c>
       <c r="D45">
-        <v>491.1212673770015</v>
+        <v>491.9621467891351</v>
       </c>
       <c r="E45">
-        <v>-9.338000000000022</v>
+        <v>-4.903999999999996</v>
       </c>
       <c r="F45">
-        <v>190.662</v>
+        <v>195.096</v>
       </c>
       <c r="G45">
         <v>12.9</v>
@@ -4977,28 +4977,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M45">
-        <v>10.200417</v>
+        <v>10.437636</v>
       </c>
       <c r="N45">
-        <v>79.27458299999999</v>
+        <v>79.037364</v>
       </c>
       <c r="O45">
-        <v>15.8549166</v>
+        <v>15.8074728</v>
       </c>
       <c r="P45">
-        <v>63.4196664</v>
+        <v>63.2298912</v>
       </c>
       <c r="Q45">
-        <v>65.0696664</v>
+        <v>64.8798912</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1498782626668881</v>
+        <v>0.1515049938745606</v>
       </c>
       <c r="T45">
-        <v>1.139699635376694</v>
+        <v>1.157513008858668</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.771700215785296</v>
+        <v>8.572343392699267</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1036747965697539</v>
+        <v>0.1035149834193817</v>
       </c>
       <c r="C46">
-        <v>309.7661467891351</v>
+        <v>306.1759105841774</v>
       </c>
       <c r="D46">
-        <v>491.9621467891351</v>
+        <v>492.8059105841774</v>
       </c>
       <c r="E46">
-        <v>-4.903999999999996</v>
+        <v>-0.4699999999999989</v>
       </c>
       <c r="F46">
-        <v>195.096</v>
+        <v>199.53</v>
       </c>
       <c r="G46">
         <v>12.9</v>
@@ -5059,28 +5059,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M46">
-        <v>10.437636</v>
+        <v>10.674855</v>
       </c>
       <c r="N46">
-        <v>79.037364</v>
+        <v>78.800145</v>
       </c>
       <c r="O46">
-        <v>15.8074728</v>
+        <v>15.760029</v>
       </c>
       <c r="P46">
-        <v>63.2298912</v>
+        <v>63.040116</v>
       </c>
       <c r="Q46">
-        <v>64.8798912</v>
+        <v>64.690116</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1515049938745606</v>
+        <v>0.1531908789443303</v>
       </c>
       <c r="T46">
-        <v>1.157513008858668</v>
+        <v>1.17597414137635</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.572343392699267</v>
+        <v>8.381846872861505</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1035149834193817</v>
+        <v>0.1033551702690094</v>
       </c>
       <c r="C47">
-        <v>306.1759105841774</v>
+        <v>302.5885736286327</v>
       </c>
       <c r="D47">
-        <v>492.8059105841774</v>
+        <v>493.6525736286328</v>
       </c>
       <c r="E47">
-        <v>-0.4699999999999989</v>
+        <v>3.963999999999999</v>
       </c>
       <c r="F47">
-        <v>199.53</v>
+        <v>203.964</v>
       </c>
       <c r="G47">
         <v>12.9</v>
@@ -5141,28 +5141,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M47">
-        <v>10.674855</v>
+        <v>10.912074</v>
       </c>
       <c r="N47">
-        <v>78.800145</v>
+        <v>78.56292599999999</v>
       </c>
       <c r="O47">
-        <v>15.760029</v>
+        <v>15.7125852</v>
       </c>
       <c r="P47">
-        <v>63.040116</v>
+        <v>62.85034079999999</v>
       </c>
       <c r="Q47">
-        <v>64.690116</v>
+        <v>64.50034079999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1531908789443303</v>
+        <v>0.1549392042018692</v>
       </c>
       <c r="T47">
-        <v>1.17597414137635</v>
+        <v>1.195119019542835</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.381846872861505</v>
+        <v>8.199632810407993</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1033551702690094</v>
+        <v>0.1031953571186371</v>
       </c>
       <c r="C48">
-        <v>302.5885736286327</v>
+        <v>299.0041508913466</v>
       </c>
       <c r="D48">
-        <v>493.6525736286328</v>
+        <v>494.5021508913467</v>
       </c>
       <c r="E48">
-        <v>3.963999999999999</v>
+        <v>8.397999999999996</v>
       </c>
       <c r="F48">
-        <v>203.964</v>
+        <v>208.398</v>
       </c>
       <c r="G48">
         <v>12.9</v>
@@ -5223,28 +5223,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M48">
-        <v>10.912074</v>
+        <v>11.149293</v>
       </c>
       <c r="N48">
-        <v>78.56292599999999</v>
+        <v>78.32570699999999</v>
       </c>
       <c r="O48">
-        <v>15.7125852</v>
+        <v>15.6651414</v>
       </c>
       <c r="P48">
-        <v>62.85034079999999</v>
+        <v>62.6605656</v>
       </c>
       <c r="Q48">
-        <v>64.50034079999999</v>
+        <v>64.3105656</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1549392042018692</v>
+        <v>0.1567535039974285</v>
       </c>
       <c r="T48">
-        <v>1.195119019542835</v>
+        <v>1.214986345942018</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.199632810407993</v>
+        <v>8.025172537846121</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1031953571186371</v>
+        <v>0.1030355439682649</v>
       </c>
       <c r="C49">
-        <v>299.0041508913466</v>
+        <v>295.4226574443882</v>
       </c>
       <c r="D49">
-        <v>494.5021508913467</v>
+        <v>495.3546574443882</v>
       </c>
       <c r="E49">
-        <v>8.397999999999996</v>
+        <v>12.83199999999999</v>
       </c>
       <c r="F49">
-        <v>208.398</v>
+        <v>212.832</v>
       </c>
       <c r="G49">
         <v>12.9</v>
@@ -5305,28 +5305,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M49">
-        <v>11.149293</v>
+        <v>11.386512</v>
       </c>
       <c r="N49">
-        <v>78.32570699999999</v>
+        <v>78.088488</v>
       </c>
       <c r="O49">
-        <v>15.6651414</v>
+        <v>15.6176976</v>
       </c>
       <c r="P49">
-        <v>62.6605656</v>
+        <v>62.4707904</v>
       </c>
       <c r="Q49">
-        <v>64.3105656</v>
+        <v>64.1207904</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1567535039974285</v>
+        <v>0.1586375845543555</v>
       </c>
       <c r="T49">
-        <v>1.214986345942018</v>
+        <v>1.23561780027963</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.025172537846121</v>
+        <v>7.85798144330766</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1030355439682649</v>
+        <v>0.1028757308178926</v>
       </c>
       <c r="C50">
-        <v>295.4226574443882</v>
+        <v>291.8441084639409</v>
       </c>
       <c r="D50">
-        <v>495.3546574443882</v>
+        <v>496.2101084639409</v>
       </c>
       <c r="E50">
-        <v>12.83199999999999</v>
+        <v>17.26599999999999</v>
       </c>
       <c r="F50">
-        <v>212.832</v>
+        <v>217.266</v>
       </c>
       <c r="G50">
         <v>12.9</v>
@@ -5387,28 +5387,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M50">
-        <v>11.386512</v>
+        <v>11.623731</v>
       </c>
       <c r="N50">
-        <v>78.088488</v>
+        <v>77.851269</v>
       </c>
       <c r="O50">
-        <v>15.6176976</v>
+        <v>15.5702538</v>
       </c>
       <c r="P50">
-        <v>62.4707904</v>
+        <v>62.2810152</v>
       </c>
       <c r="Q50">
-        <v>64.1207904</v>
+        <v>63.9310152</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1586375845543555</v>
+        <v>0.1605955506233188</v>
       </c>
       <c r="T50">
-        <v>1.23561780027963</v>
+        <v>1.257058331257934</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.85798144330766</v>
+        <v>7.697614475076893</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1028757308178926</v>
+        <v>0.1030359176675203</v>
       </c>
       <c r="C51">
-        <v>291.8441084639409</v>
+        <v>286.5526605561414</v>
       </c>
       <c r="D51">
-        <v>496.2101084639409</v>
+        <v>495.3526605561414</v>
       </c>
       <c r="E51">
-        <v>17.26599999999999</v>
+        <v>21.69999999999999</v>
       </c>
       <c r="F51">
-        <v>217.266</v>
+        <v>221.7</v>
       </c>
       <c r="G51">
         <v>12.9</v>
@@ -5469,45 +5469,45 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M51">
-        <v>11.623731</v>
+        <v>12.03831</v>
       </c>
       <c r="N51">
-        <v>77.851269</v>
+        <v>77.43669</v>
       </c>
       <c r="O51">
-        <v>15.5702538</v>
+        <v>15.487338</v>
       </c>
       <c r="P51">
-        <v>62.2810152</v>
+        <v>61.949352</v>
       </c>
       <c r="Q51">
-        <v>63.9310152</v>
+        <v>63.599352</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1605955506233188</v>
+        <v>0.1626318353350407</v>
       </c>
       <c r="T51">
-        <v>1.257058331257934</v>
+        <v>1.279356483475369</v>
       </c>
       <c r="U51">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.697614475076893</v>
+        <v>7.432521674553986</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1030359176675203</v>
+        <v>0.1028825045171481</v>
       </c>
       <c r="C52">
-        <v>286.5526605561414</v>
+        <v>282.9397901135145</v>
       </c>
       <c r="D52">
-        <v>495.3526605561414</v>
+        <v>496.1737901135145</v>
       </c>
       <c r="E52">
-        <v>21.69999999999999</v>
+        <v>26.13399999999999</v>
       </c>
       <c r="F52">
-        <v>221.7</v>
+        <v>226.134</v>
       </c>
       <c r="G52">
         <v>12.9</v>
@@ -5551,28 +5551,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M52">
-        <v>12.03831</v>
+        <v>12.2790762</v>
       </c>
       <c r="N52">
-        <v>77.43669</v>
+        <v>77.1959238</v>
       </c>
       <c r="O52">
-        <v>15.487338</v>
+        <v>15.43918476</v>
       </c>
       <c r="P52">
-        <v>61.949352</v>
+        <v>61.75673904</v>
       </c>
       <c r="Q52">
-        <v>63.599352</v>
+        <v>63.40673904</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1626318353350407</v>
+        <v>0.1647512337084654</v>
       </c>
       <c r="T52">
-        <v>1.279356483475369</v>
+        <v>1.302564764354741</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.432521674553986</v>
+        <v>7.286785955445086</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1028825045171481</v>
+        <v>0.1027290913667758</v>
       </c>
       <c r="C53">
-        <v>282.9397901135145</v>
+        <v>279.3296465091484</v>
       </c>
       <c r="D53">
-        <v>496.1737901135145</v>
+        <v>496.9976465091484</v>
       </c>
       <c r="E53">
-        <v>26.13399999999999</v>
+        <v>30.56799999999998</v>
       </c>
       <c r="F53">
-        <v>226.134</v>
+        <v>230.568</v>
       </c>
       <c r="G53">
         <v>12.9</v>
@@ -5633,28 +5633,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M53">
-        <v>12.2790762</v>
+        <v>12.5198424</v>
       </c>
       <c r="N53">
-        <v>77.1959238</v>
+        <v>76.95515759999999</v>
       </c>
       <c r="O53">
-        <v>15.43918476</v>
+        <v>15.39103152</v>
       </c>
       <c r="P53">
-        <v>61.75673904</v>
+        <v>61.56412607999999</v>
       </c>
       <c r="Q53">
-        <v>63.40673904</v>
+        <v>63.21412607999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1647512337084654</v>
+        <v>0.1669589403474496</v>
       </c>
       <c r="T53">
-        <v>1.302564764354741</v>
+        <v>1.32674005693742</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.286785955445086</v>
+        <v>7.146655456301909</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1027290913667758</v>
+        <v>0.1025756782164035</v>
       </c>
       <c r="C54">
-        <v>279.3296465091484</v>
+        <v>275.7222433487168</v>
       </c>
       <c r="D54">
-        <v>496.9976465091484</v>
+        <v>497.8242433487168</v>
       </c>
       <c r="E54">
-        <v>30.56799999999998</v>
+        <v>35.00200000000001</v>
       </c>
       <c r="F54">
-        <v>230.568</v>
+        <v>235.002</v>
       </c>
       <c r="G54">
         <v>12.9</v>
@@ -5715,28 +5715,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M54">
-        <v>12.5198424</v>
+        <v>12.7606086</v>
       </c>
       <c r="N54">
-        <v>76.95515759999999</v>
+        <v>76.7143914</v>
       </c>
       <c r="O54">
-        <v>15.39103152</v>
+        <v>15.34287828</v>
       </c>
       <c r="P54">
-        <v>61.56412607999999</v>
+        <v>61.37151312</v>
       </c>
       <c r="Q54">
-        <v>63.21412607999999</v>
+        <v>63.02151311999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1669589403474496</v>
+        <v>0.1692605919497947</v>
       </c>
       <c r="T54">
-        <v>1.32674005693742</v>
+        <v>1.351944085374681</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.146655456301909</v>
+        <v>7.011812900522628</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1025756782164035</v>
+        <v>0.1024222650660313</v>
       </c>
       <c r="C55">
-        <v>275.7222433487168</v>
+        <v>272.1175943285584</v>
       </c>
       <c r="D55">
-        <v>497.8242433487168</v>
+        <v>498.6535943285584</v>
       </c>
       <c r="E55">
-        <v>35.00200000000001</v>
+        <v>39.43600000000001</v>
       </c>
       <c r="F55">
-        <v>235.002</v>
+        <v>239.436</v>
       </c>
       <c r="G55">
         <v>12.9</v>
@@ -5797,28 +5797,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M55">
-        <v>12.7606086</v>
+        <v>13.0013748</v>
       </c>
       <c r="N55">
-        <v>76.7143914</v>
+        <v>76.47362519999999</v>
       </c>
       <c r="O55">
-        <v>15.34287828</v>
+        <v>15.29472504</v>
       </c>
       <c r="P55">
-        <v>61.37151312</v>
+        <v>61.17890015999999</v>
       </c>
       <c r="Q55">
-        <v>63.02151311999999</v>
+        <v>62.82890015999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1692605919497947</v>
+        <v>0.1716623153609375</v>
       </c>
       <c r="T55">
-        <v>1.351944085374681</v>
+        <v>1.378243941135301</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.011812900522628</v>
+        <v>6.881964513475912</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1024222650660313</v>
+        <v>0.102268851915659</v>
       </c>
       <c r="C56">
-        <v>272.1175943285584</v>
+        <v>268.5157132364345</v>
       </c>
       <c r="D56">
-        <v>498.6535943285584</v>
+        <v>499.4857132364345</v>
       </c>
       <c r="E56">
-        <v>39.43600000000001</v>
+        <v>43.87</v>
       </c>
       <c r="F56">
-        <v>239.436</v>
+        <v>243.87</v>
       </c>
       <c r="G56">
         <v>12.9</v>
@@ -5879,28 +5879,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M56">
-        <v>13.0013748</v>
+        <v>13.242141</v>
       </c>
       <c r="N56">
-        <v>76.47362519999999</v>
+        <v>76.23285899999999</v>
       </c>
       <c r="O56">
-        <v>15.29472504</v>
+        <v>15.2465718</v>
       </c>
       <c r="P56">
-        <v>61.17890015999999</v>
+        <v>60.98628719999999</v>
       </c>
       <c r="Q56">
-        <v>62.82890015999999</v>
+        <v>62.63628719999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1716623153609375</v>
+        <v>0.1741707820347978</v>
       </c>
       <c r="T56">
-        <v>1.378243941135301</v>
+        <v>1.405712679374171</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.881964513475912</v>
+        <v>6.756837885958169</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.102268851915659</v>
+        <v>0.1021154387652867</v>
       </c>
       <c r="C57">
-        <v>268.5157132364345</v>
+        <v>264.9166139522922</v>
       </c>
       <c r="D57">
-        <v>499.4857132364345</v>
+        <v>500.3206139522921</v>
       </c>
       <c r="E57">
-        <v>43.87</v>
+        <v>48.304</v>
       </c>
       <c r="F57">
-        <v>243.87</v>
+        <v>248.304</v>
       </c>
       <c r="G57">
         <v>12.9</v>
@@ -5961,28 +5961,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M57">
-        <v>13.242141</v>
+        <v>13.4829072</v>
       </c>
       <c r="N57">
-        <v>76.23285899999999</v>
+        <v>75.99209279999999</v>
       </c>
       <c r="O57">
-        <v>15.2465718</v>
+        <v>15.19841856</v>
       </c>
       <c r="P57">
-        <v>60.98628719999999</v>
+        <v>60.79367423999999</v>
       </c>
       <c r="Q57">
-        <v>62.63628719999999</v>
+        <v>62.44367423999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1741707820347978</v>
+        <v>0.1767932699211062</v>
       </c>
       <c r="T57">
-        <v>1.405712679374171</v>
+        <v>1.434429996623899</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.756837885958169</v>
+        <v>6.636180066566059</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1021154387652867</v>
+        <v>0.1019620256149145</v>
       </c>
       <c r="C58">
-        <v>264.9166139522922</v>
+        <v>261.3203104490361</v>
       </c>
       <c r="D58">
-        <v>500.3206139522921</v>
+        <v>501.1583104490362</v>
       </c>
       <c r="E58">
-        <v>48.304</v>
+        <v>52.73800000000003</v>
       </c>
       <c r="F58">
-        <v>248.304</v>
+        <v>252.738</v>
       </c>
       <c r="G58">
         <v>12.9</v>
@@ -6043,28 +6043,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M58">
-        <v>13.4829072</v>
+        <v>13.7236734</v>
       </c>
       <c r="N58">
-        <v>75.99209279999999</v>
+        <v>75.7513266</v>
       </c>
       <c r="O58">
-        <v>15.19841856</v>
+        <v>15.15026532</v>
       </c>
       <c r="P58">
-        <v>60.79367423999999</v>
+        <v>60.60106128</v>
       </c>
       <c r="Q58">
-        <v>62.44367423999999</v>
+        <v>62.25106127999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1767932699211062</v>
+        <v>0.1795377339881732</v>
       </c>
       <c r="T58">
-        <v>1.434429996623899</v>
+        <v>1.464483003048033</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.636180066566059</v>
+        <v>6.519755854871917</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1019620256149145</v>
+        <v>0.1018086124645422</v>
       </c>
       <c r="C59">
-        <v>261.3203104490361</v>
+        <v>257.726816793309</v>
       </c>
       <c r="D59">
-        <v>501.1583104490362</v>
+        <v>501.9988167933091</v>
       </c>
       <c r="E59">
-        <v>52.73800000000003</v>
+        <v>57.17200000000003</v>
       </c>
       <c r="F59">
-        <v>252.738</v>
+        <v>257.172</v>
       </c>
       <c r="G59">
         <v>12.9</v>
@@ -6125,28 +6125,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M59">
-        <v>13.7236734</v>
+        <v>13.9644396</v>
       </c>
       <c r="N59">
-        <v>75.7513266</v>
+        <v>75.51056039999999</v>
       </c>
       <c r="O59">
-        <v>15.15026532</v>
+        <v>15.10211208</v>
       </c>
       <c r="P59">
-        <v>60.60106128</v>
+        <v>60.40844831999999</v>
       </c>
       <c r="Q59">
-        <v>62.25106127999999</v>
+        <v>62.05844831999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1795377339881732</v>
+        <v>0.1824128868203386</v>
       </c>
       <c r="T59">
-        <v>1.464483003048033</v>
+        <v>1.495967105016173</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.519755854871917</v>
+        <v>6.407346271167228</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1018086124645422</v>
+        <v>0.1016551993141699</v>
       </c>
       <c r="C60">
-        <v>257.7268167933092</v>
+        <v>254.1361471462778</v>
       </c>
       <c r="D60">
-        <v>501.9988167933092</v>
+        <v>502.8421471462778</v>
       </c>
       <c r="E60">
-        <v>57.17199999999997</v>
+        <v>61.60599999999999</v>
       </c>
       <c r="F60">
-        <v>257.172</v>
+        <v>261.606</v>
       </c>
       <c r="G60">
         <v>12.9</v>
@@ -6207,28 +6207,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M60">
-        <v>13.9644396</v>
+        <v>14.2052058</v>
       </c>
       <c r="N60">
-        <v>75.5105604</v>
+        <v>75.26979419999999</v>
       </c>
       <c r="O60">
-        <v>15.10211208</v>
+        <v>15.05395884</v>
       </c>
       <c r="P60">
-        <v>60.40844832000001</v>
+        <v>60.21583535999999</v>
       </c>
       <c r="Q60">
-        <v>62.05844832</v>
+        <v>61.86583535999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1824128868203385</v>
+        <v>0.1854282910101706</v>
       </c>
       <c r="T60">
-        <v>1.495967105016172</v>
+        <v>1.528987016836417</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.40734627116723</v>
+        <v>6.298747181825412</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1016551993141699</v>
+        <v>0.1015017861637977</v>
       </c>
       <c r="C61">
-        <v>254.1361471462778</v>
+        <v>250.5483157644298</v>
       </c>
       <c r="D61">
-        <v>502.8421471462778</v>
+        <v>503.6883157644298</v>
       </c>
       <c r="E61">
-        <v>61.60599999999999</v>
+        <v>66.03999999999996</v>
       </c>
       <c r="F61">
-        <v>261.606</v>
+        <v>266.04</v>
       </c>
       <c r="G61">
         <v>12.9</v>
@@ -6289,28 +6289,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M61">
-        <v>14.2052058</v>
+        <v>14.445972</v>
       </c>
       <c r="N61">
-        <v>75.26979419999999</v>
+        <v>75.029028</v>
       </c>
       <c r="O61">
-        <v>15.05395884</v>
+        <v>15.0058056</v>
       </c>
       <c r="P61">
-        <v>60.21583535999999</v>
+        <v>60.02322239999999</v>
       </c>
       <c r="Q61">
-        <v>61.86583535999999</v>
+        <v>61.67322239999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1854282910101706</v>
+        <v>0.1885944654094941</v>
       </c>
       <c r="T61">
-        <v>1.528987016836417</v>
+        <v>1.563657924247674</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.298747181825412</v>
+        <v>6.193768062128322</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1015017861637977</v>
+        <v>0.1018363730134254</v>
       </c>
       <c r="C62">
-        <v>250.5483157644298</v>
+        <v>244.2725159061005</v>
       </c>
       <c r="D62">
-        <v>503.6883157644298</v>
+        <v>501.8465159061005</v>
       </c>
       <c r="E62">
-        <v>66.03999999999996</v>
+        <v>70.47399999999999</v>
       </c>
       <c r="F62">
-        <v>266.04</v>
+        <v>270.474</v>
       </c>
       <c r="G62">
         <v>12.9</v>
@@ -6371,45 +6371,45 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M62">
-        <v>14.445972</v>
+        <v>14.9572122</v>
       </c>
       <c r="N62">
-        <v>75.029028</v>
+        <v>74.51778779999999</v>
       </c>
       <c r="O62">
-        <v>15.0058056</v>
+        <v>14.90355756</v>
       </c>
       <c r="P62">
-        <v>60.02322239999999</v>
+        <v>59.61423024</v>
       </c>
       <c r="Q62">
-        <v>61.67322239999999</v>
+        <v>61.26423024</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1885944654094941</v>
+        <v>0.1919230077267318</v>
       </c>
       <c r="T62">
-        <v>1.563657924247674</v>
+        <v>1.60010682691079</v>
       </c>
       <c r="U62">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>6.193768062128322</v>
+        <v>5.982063957078846</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1018363730134254</v>
+        <v>0.1016909598630531</v>
       </c>
       <c r="C63">
-        <v>244.2725159061005</v>
+        <v>240.6373139866456</v>
       </c>
       <c r="D63">
-        <v>501.8465159061005</v>
+        <v>502.6453139866455</v>
       </c>
       <c r="E63">
-        <v>70.47399999999999</v>
+        <v>74.90799999999996</v>
       </c>
       <c r="F63">
-        <v>270.474</v>
+        <v>274.908</v>
       </c>
       <c r="G63">
         <v>12.9</v>
@@ -6453,28 +6453,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M63">
-        <v>14.9572122</v>
+        <v>15.2024124</v>
       </c>
       <c r="N63">
-        <v>74.51778779999999</v>
+        <v>74.27258759999999</v>
       </c>
       <c r="O63">
-        <v>14.90355756</v>
+        <v>14.85451752</v>
       </c>
       <c r="P63">
-        <v>59.61423024</v>
+        <v>59.41807007999999</v>
       </c>
       <c r="Q63">
-        <v>61.26423024</v>
+        <v>61.06807007999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1919230077267318</v>
+        <v>0.1954267364817187</v>
       </c>
       <c r="T63">
-        <v>1.60010682691079</v>
+        <v>1.638474092871964</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.982063957078846</v>
+        <v>5.885579054545317</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1016909598630531</v>
+        <v>0.1015455467126809</v>
       </c>
       <c r="C64">
-        <v>240.6373139866456</v>
+        <v>237.0046590436592</v>
       </c>
       <c r="D64">
-        <v>502.6453139866455</v>
+        <v>503.4466590436592</v>
       </c>
       <c r="E64">
-        <v>74.90799999999996</v>
+        <v>79.34199999999998</v>
       </c>
       <c r="F64">
-        <v>274.908</v>
+        <v>279.342</v>
       </c>
       <c r="G64">
         <v>12.9</v>
@@ -6535,28 +6535,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M64">
-        <v>15.2024124</v>
+        <v>15.4476126</v>
       </c>
       <c r="N64">
-        <v>74.27258759999999</v>
+        <v>74.02738739999999</v>
       </c>
       <c r="O64">
-        <v>14.85451752</v>
+        <v>14.80547748</v>
       </c>
       <c r="P64">
-        <v>59.41807007999999</v>
+        <v>59.22190991999999</v>
       </c>
       <c r="Q64">
-        <v>61.06807007999999</v>
+        <v>60.87190991999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1954267364817187</v>
+        <v>0.1991198559802185</v>
       </c>
       <c r="T64">
-        <v>1.638474092871964</v>
+        <v>1.678915265101311</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.885579054545317</v>
+        <v>5.792157164790629</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1015455467126809</v>
+        <v>0.1014001335623086</v>
       </c>
       <c r="C65">
-        <v>237.0046590436592</v>
+        <v>233.3745632781868</v>
       </c>
       <c r="D65">
-        <v>503.4466590436592</v>
+        <v>504.2505632781868</v>
       </c>
       <c r="E65">
-        <v>79.34199999999998</v>
+        <v>83.77600000000001</v>
       </c>
       <c r="F65">
-        <v>279.342</v>
+        <v>283.776</v>
       </c>
       <c r="G65">
         <v>12.9</v>
@@ -6617,28 +6617,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M65">
-        <v>15.4476126</v>
+        <v>15.6928128</v>
       </c>
       <c r="N65">
-        <v>74.02738739999999</v>
+        <v>73.7821872</v>
       </c>
       <c r="O65">
-        <v>14.80547748</v>
+        <v>14.75643744</v>
       </c>
       <c r="P65">
-        <v>59.22190991999999</v>
+        <v>59.02574976</v>
       </c>
       <c r="Q65">
-        <v>60.87190991999999</v>
+        <v>60.67574976</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1991198559802185</v>
+        <v>0.2030181487841905</v>
       </c>
       <c r="T65">
-        <v>1.678915265101311</v>
+        <v>1.721603169121176</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.792157164790629</v>
+        <v>5.701654709090775</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1014001335623086</v>
+        <v>0.1012547204119363</v>
       </c>
       <c r="C66">
-        <v>233.3745632781868</v>
+        <v>229.747038969329</v>
       </c>
       <c r="D66">
-        <v>504.2505632781868</v>
+        <v>505.057038969329</v>
       </c>
       <c r="E66">
-        <v>83.77600000000001</v>
+        <v>88.20999999999998</v>
       </c>
       <c r="F66">
-        <v>283.776</v>
+        <v>288.21</v>
       </c>
       <c r="G66">
         <v>12.9</v>
@@ -6699,28 +6699,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M66">
-        <v>15.6928128</v>
+        <v>15.938013</v>
       </c>
       <c r="N66">
-        <v>73.7821872</v>
+        <v>73.536987</v>
       </c>
       <c r="O66">
-        <v>14.75643744</v>
+        <v>14.7073974</v>
       </c>
       <c r="P66">
-        <v>59.02574976</v>
+        <v>58.8295896</v>
       </c>
       <c r="Q66">
-        <v>60.67574976</v>
+        <v>60.4795896</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2030181487841905</v>
+        <v>0.2071392011769609</v>
       </c>
       <c r="T66">
-        <v>1.721603169121176</v>
+        <v>1.766730381942177</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.701654709090775</v>
+        <v>5.613936944335533</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1012547204119363</v>
+        <v>0.101109307261564</v>
       </c>
       <c r="C67">
-        <v>229.747038969329</v>
+        <v>226.1220984748666</v>
       </c>
       <c r="D67">
-        <v>505.057038969329</v>
+        <v>505.8660984748666</v>
       </c>
       <c r="E67">
-        <v>88.20999999999998</v>
+        <v>92.64400000000001</v>
       </c>
       <c r="F67">
-        <v>288.21</v>
+        <v>292.644</v>
       </c>
       <c r="G67">
         <v>12.9</v>
@@ -6781,28 +6781,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M67">
-        <v>15.938013</v>
+        <v>16.1832132</v>
       </c>
       <c r="N67">
-        <v>73.536987</v>
+        <v>73.2917868</v>
       </c>
       <c r="O67">
-        <v>14.7073974</v>
+        <v>14.65835736</v>
       </c>
       <c r="P67">
-        <v>58.8295896</v>
+        <v>58.63342944</v>
       </c>
       <c r="Q67">
-        <v>60.4795896</v>
+        <v>60.28342944</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2071392011769609</v>
+        <v>0.2115026684163648</v>
       </c>
       <c r="T67">
-        <v>1.766730381942177</v>
+        <v>1.814512136693825</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.613936944335533</v>
+        <v>5.528877293663782</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.101109307261564</v>
+        <v>0.1009638941111918</v>
       </c>
       <c r="C68">
-        <v>226.1220984748666</v>
+        <v>222.4997542318921</v>
       </c>
       <c r="D68">
-        <v>505.8660984748666</v>
+        <v>506.677754231892</v>
       </c>
       <c r="E68">
-        <v>92.64400000000001</v>
+        <v>97.07799999999997</v>
       </c>
       <c r="F68">
-        <v>292.644</v>
+        <v>297.078</v>
       </c>
       <c r="G68">
         <v>12.9</v>
@@ -6863,28 +6863,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M68">
-        <v>16.1832132</v>
+        <v>16.4284134</v>
       </c>
       <c r="N68">
-        <v>73.2917868</v>
+        <v>73.0465866</v>
       </c>
       <c r="O68">
-        <v>14.65835736</v>
+        <v>14.60931732</v>
       </c>
       <c r="P68">
-        <v>58.63342944</v>
+        <v>58.43726928</v>
       </c>
       <c r="Q68">
-        <v>60.28342944</v>
+        <v>60.08726927999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2115026684163648</v>
+        <v>0.2161305882157327</v>
       </c>
       <c r="T68">
-        <v>1.814512136693825</v>
+        <v>1.865189755369815</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.528877293663782</v>
+        <v>5.446356737041935</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1009638941111918</v>
+        <v>0.1008184809608195</v>
       </c>
       <c r="C69">
-        <v>222.4997542318921</v>
+        <v>218.8800187574472</v>
       </c>
       <c r="D69">
-        <v>506.677754231892</v>
+        <v>507.4920187574472</v>
       </c>
       <c r="E69">
-        <v>97.07799999999997</v>
+        <v>101.512</v>
       </c>
       <c r="F69">
-        <v>297.078</v>
+        <v>301.512</v>
       </c>
       <c r="G69">
         <v>12.9</v>
@@ -6945,28 +6945,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M69">
-        <v>16.4284134</v>
+        <v>16.6736136</v>
       </c>
       <c r="N69">
-        <v>73.0465866</v>
+        <v>72.8013864</v>
       </c>
       <c r="O69">
-        <v>14.60931732</v>
+        <v>14.56027728</v>
       </c>
       <c r="P69">
-        <v>58.43726928</v>
+        <v>58.24110912</v>
       </c>
       <c r="Q69">
-        <v>60.08726927999999</v>
+        <v>59.89110912</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2161305882157327</v>
+        <v>0.221047753002561</v>
       </c>
       <c r="T69">
-        <v>1.865189755369815</v>
+        <v>1.919034725213054</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.446356737041935</v>
+        <v>5.366263255614848</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1008184809608195</v>
+        <v>0.1006730678104472</v>
       </c>
       <c r="C70">
-        <v>218.8800187574472</v>
+        <v>215.2629046491655</v>
       </c>
       <c r="D70">
-        <v>507.4920187574472</v>
+        <v>508.3089046491656</v>
       </c>
       <c r="E70">
-        <v>101.512</v>
+        <v>105.946</v>
       </c>
       <c r="F70">
-        <v>301.512</v>
+        <v>305.946</v>
       </c>
       <c r="G70">
         <v>12.9</v>
@@ -7027,28 +7027,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M70">
-        <v>16.6736136</v>
+        <v>16.9188138</v>
       </c>
       <c r="N70">
-        <v>72.8013864</v>
+        <v>72.55618619999998</v>
       </c>
       <c r="O70">
-        <v>14.56027728</v>
+        <v>14.51123724</v>
       </c>
       <c r="P70">
-        <v>58.24110912</v>
+        <v>58.04494895999999</v>
       </c>
       <c r="Q70">
-        <v>59.89110912</v>
+        <v>59.69494895999998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.221047753002561</v>
+        <v>0.2262821542272492</v>
       </c>
       <c r="T70">
-        <v>1.919034725213054</v>
+        <v>1.976353564078438</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.366263255614848</v>
+        <v>5.288491324374052</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1006730678104472</v>
+        <v>0.100527654660075</v>
       </c>
       <c r="C71">
-        <v>215.2629046491655</v>
+        <v>211.648424585923</v>
       </c>
       <c r="D71">
-        <v>508.3089046491656</v>
+        <v>509.1284245859229</v>
       </c>
       <c r="E71">
-        <v>105.946</v>
+        <v>110.38</v>
       </c>
       <c r="F71">
-        <v>305.946</v>
+        <v>310.38</v>
       </c>
       <c r="G71">
         <v>12.9</v>
@@ -7109,28 +7109,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M71">
-        <v>16.9188138</v>
+        <v>17.164014</v>
       </c>
       <c r="N71">
-        <v>72.55618619999998</v>
+        <v>72.31098599999999</v>
       </c>
       <c r="O71">
-        <v>14.51123724</v>
+        <v>14.4621972</v>
       </c>
       <c r="P71">
-        <v>58.04494895999999</v>
+        <v>57.84878879999999</v>
       </c>
       <c r="Q71">
-        <v>59.69494895999998</v>
+        <v>59.49878879999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2262821542272492</v>
+        <v>0.2318655155335833</v>
       </c>
       <c r="T71">
-        <v>1.976353564078438</v>
+        <v>2.037493658868181</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.288491324374052</v>
+        <v>5.212941448311565</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.100527654660075</v>
+        <v>0.1003822415097027</v>
       </c>
       <c r="C72">
-        <v>211.648424585923</v>
+        <v>208.0365913284934</v>
       </c>
       <c r="D72">
-        <v>509.1284245859229</v>
+        <v>509.9505913284934</v>
       </c>
       <c r="E72">
-        <v>110.38</v>
+        <v>114.814</v>
       </c>
       <c r="F72">
-        <v>310.38</v>
+        <v>314.814</v>
       </c>
       <c r="G72">
         <v>12.9</v>
@@ -7191,28 +7191,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M72">
-        <v>17.164014</v>
+        <v>17.4092142</v>
       </c>
       <c r="N72">
-        <v>72.31098599999999</v>
+        <v>72.06578579999999</v>
       </c>
       <c r="O72">
-        <v>14.4621972</v>
+        <v>14.41315716</v>
       </c>
       <c r="P72">
-        <v>57.84878879999999</v>
+        <v>57.65262863999999</v>
       </c>
       <c r="Q72">
-        <v>59.49878879999999</v>
+        <v>59.30262863999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2318655155335833</v>
+        <v>0.2378339362403542</v>
       </c>
       <c r="T72">
-        <v>2.037493658868181</v>
+        <v>2.102850311919286</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.212941448311565</v>
+        <v>5.139519737771966</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1003822415097027</v>
+        <v>0.1002368283593304</v>
       </c>
       <c r="C73">
-        <v>208.0365913284935</v>
+        <v>204.4274177202111</v>
       </c>
       <c r="D73">
-        <v>509.9505913284934</v>
+        <v>510.775417720211</v>
       </c>
       <c r="E73">
-        <v>114.814</v>
+        <v>119.248</v>
       </c>
       <c r="F73">
-        <v>314.814</v>
+        <v>319.248</v>
       </c>
       <c r="G73">
         <v>12.9</v>
@@ -7273,28 +7273,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M73">
-        <v>17.4092142</v>
+        <v>17.6544144</v>
       </c>
       <c r="N73">
-        <v>72.0657858</v>
+        <v>71.82058559999999</v>
       </c>
       <c r="O73">
-        <v>14.41315716</v>
+        <v>14.36411712</v>
       </c>
       <c r="P73">
-        <v>57.65262864</v>
+        <v>57.45646847999999</v>
       </c>
       <c r="Q73">
-        <v>59.30262864</v>
+        <v>59.10646847999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2378339362403541</v>
+        <v>0.2442286727118944</v>
       </c>
       <c r="T73">
-        <v>2.102850311919285</v>
+        <v>2.172875297331183</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.139519737771967</v>
+        <v>5.0681375191918</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1002368283593304</v>
+        <v>0.1000914152089582</v>
       </c>
       <c r="C74">
-        <v>204.4274177202111</v>
+        <v>200.8209166876392</v>
       </c>
       <c r="D74">
-        <v>510.775417720211</v>
+        <v>511.6029166876392</v>
       </c>
       <c r="E74">
-        <v>119.248</v>
+        <v>123.682</v>
       </c>
       <c r="F74">
-        <v>319.248</v>
+        <v>323.682</v>
       </c>
       <c r="G74">
         <v>12.9</v>
@@ -7355,28 +7355,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M74">
-        <v>17.6544144</v>
+        <v>17.8996146</v>
       </c>
       <c r="N74">
-        <v>71.82058559999999</v>
+        <v>71.57538539999999</v>
       </c>
       <c r="O74">
-        <v>14.36411712</v>
+        <v>14.31507708</v>
       </c>
       <c r="P74">
-        <v>57.45646847999999</v>
+        <v>57.26030831999999</v>
       </c>
       <c r="Q74">
-        <v>59.10646847999999</v>
+        <v>58.91030831999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2442286727118944</v>
+        <v>0.2510970933665117</v>
       </c>
       <c r="T74">
-        <v>2.172875297331183</v>
+        <v>2.248087318699517</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.0681375191918</v>
+        <v>4.998710977833008</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1000914152089582</v>
+        <v>0.09994600205858589</v>
       </c>
       <c r="C75">
-        <v>200.8209166876392</v>
+        <v>197.2171012412454</v>
       </c>
       <c r="D75">
-        <v>511.6029166876392</v>
+        <v>512.4331012412454</v>
       </c>
       <c r="E75">
-        <v>123.682</v>
+        <v>128.116</v>
       </c>
       <c r="F75">
-        <v>323.682</v>
+        <v>328.116</v>
       </c>
       <c r="G75">
         <v>12.9</v>
@@ -7437,28 +7437,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M75">
-        <v>17.8996146</v>
+        <v>18.1448148</v>
       </c>
       <c r="N75">
-        <v>71.57538539999999</v>
+        <v>71.33018519999999</v>
       </c>
       <c r="O75">
-        <v>14.31507708</v>
+        <v>14.26603704</v>
       </c>
       <c r="P75">
-        <v>57.26030831999999</v>
+        <v>57.06414815999999</v>
       </c>
       <c r="Q75">
-        <v>58.91030831999999</v>
+        <v>58.71414815999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2510970933665117</v>
+        <v>0.2584938540714842</v>
       </c>
       <c r="T75">
-        <v>2.248087318699517</v>
+        <v>2.329084880173108</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.998710977833008</v>
+        <v>4.931160829483914</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09994600205858589</v>
+        <v>0.09980058890821364</v>
       </c>
       <c r="C76">
-        <v>197.2171012412454</v>
+        <v>193.6159844760837</v>
       </c>
       <c r="D76">
-        <v>512.4331012412454</v>
+        <v>513.2659844760836</v>
       </c>
       <c r="E76">
-        <v>128.116</v>
+        <v>132.55</v>
       </c>
       <c r="F76">
-        <v>328.116</v>
+        <v>332.55</v>
       </c>
       <c r="G76">
         <v>12.9</v>
@@ -7519,28 +7519,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M76">
-        <v>18.1448148</v>
+        <v>18.390015</v>
       </c>
       <c r="N76">
-        <v>71.33018519999999</v>
+        <v>71.08498499999999</v>
       </c>
       <c r="O76">
-        <v>14.26603704</v>
+        <v>14.216997</v>
       </c>
       <c r="P76">
-        <v>57.06414815999999</v>
+        <v>56.86798799999999</v>
       </c>
       <c r="Q76">
-        <v>58.71414815999999</v>
+        <v>58.51798799999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2584938540714842</v>
+        <v>0.2664823556328546</v>
       </c>
       <c r="T76">
-        <v>2.329084880173108</v>
+        <v>2.416562246564587</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.931160829483914</v>
+        <v>4.865412018424129</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09980058890821364</v>
+        <v>0.09965517575784136</v>
       </c>
       <c r="C77">
-        <v>193.6159844760837</v>
+        <v>190.017579572483</v>
       </c>
       <c r="D77">
-        <v>513.2659844760836</v>
+        <v>514.101579572483</v>
       </c>
       <c r="E77">
-        <v>132.55</v>
+        <v>136.984</v>
       </c>
       <c r="F77">
-        <v>332.55</v>
+        <v>336.984</v>
       </c>
       <c r="G77">
         <v>12.9</v>
@@ -7601,28 +7601,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M77">
-        <v>18.390015</v>
+        <v>18.6352152</v>
       </c>
       <c r="N77">
-        <v>71.08498499999999</v>
+        <v>70.83978479999999</v>
       </c>
       <c r="O77">
-        <v>14.216997</v>
+        <v>14.16795696</v>
       </c>
       <c r="P77">
-        <v>56.86798799999999</v>
+        <v>56.67182783999999</v>
       </c>
       <c r="Q77">
-        <v>58.51798799999999</v>
+        <v>58.32182783999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2664823556328546</v>
+        <v>0.2751365656576724</v>
       </c>
       <c r="T77">
-        <v>2.416562246564587</v>
+        <v>2.511329393488688</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.865412018424129</v>
+        <v>4.801393439234337</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09965517575784136</v>
+        <v>0.0995097626074691</v>
       </c>
       <c r="C78">
-        <v>190.017579572483</v>
+        <v>186.4218997967419</v>
       </c>
       <c r="D78">
-        <v>514.101579572483</v>
+        <v>514.9398997967419</v>
       </c>
       <c r="E78">
-        <v>136.984</v>
+        <v>141.418</v>
       </c>
       <c r="F78">
-        <v>336.984</v>
+        <v>341.418</v>
       </c>
       <c r="G78">
         <v>12.9</v>
@@ -7683,28 +7683,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M78">
-        <v>18.6352152</v>
+        <v>18.8804154</v>
       </c>
       <c r="N78">
-        <v>70.83978479999999</v>
+        <v>70.59458459999999</v>
       </c>
       <c r="O78">
-        <v>14.16795696</v>
+        <v>14.11891692</v>
       </c>
       <c r="P78">
-        <v>56.67182783999999</v>
+        <v>56.47566767999999</v>
       </c>
       <c r="Q78">
-        <v>58.32182783999999</v>
+        <v>58.12566767999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2751365656576724</v>
+        <v>0.2845433156846483</v>
       </c>
       <c r="T78">
-        <v>2.511329393488688</v>
+        <v>2.614337161884451</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.801393439234337</v>
+        <v>4.739037680283241</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0995097626074691</v>
+        <v>0.09936434945709684</v>
       </c>
       <c r="C79">
-        <v>186.4218997967419</v>
+        <v>182.8289585018316</v>
       </c>
       <c r="D79">
-        <v>514.9398997967419</v>
+        <v>515.7809585018316</v>
       </c>
       <c r="E79">
-        <v>141.418</v>
+        <v>145.852</v>
       </c>
       <c r="F79">
-        <v>341.418</v>
+        <v>345.852</v>
       </c>
       <c r="G79">
         <v>12.9</v>
@@ -7765,28 +7765,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M79">
-        <v>18.8804154</v>
+        <v>19.1256156</v>
       </c>
       <c r="N79">
-        <v>70.59458459999999</v>
+        <v>70.34938439999999</v>
       </c>
       <c r="O79">
-        <v>14.11891692</v>
+        <v>14.06987688</v>
       </c>
       <c r="P79">
-        <v>56.47566767999999</v>
+        <v>56.27950752</v>
       </c>
       <c r="Q79">
-        <v>58.12566767999999</v>
+        <v>57.92950751999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2845433156846483</v>
+        <v>0.2948052248049857</v>
       </c>
       <c r="T79">
-        <v>2.614337161884451</v>
+        <v>2.726709272861646</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.739037680283241</v>
+        <v>4.678280786946277</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09936434945709684</v>
+        <v>0.09921893630672457</v>
       </c>
       <c r="C80">
-        <v>182.8289585018316</v>
+        <v>179.2387691281039</v>
       </c>
       <c r="D80">
-        <v>515.7809585018316</v>
+        <v>516.6247691281039</v>
       </c>
       <c r="E80">
-        <v>145.852</v>
+        <v>150.286</v>
       </c>
       <c r="F80">
-        <v>345.852</v>
+        <v>350.286</v>
       </c>
       <c r="G80">
         <v>12.9</v>
@@ -7847,28 +7847,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M80">
-        <v>19.1256156</v>
+        <v>19.3708158</v>
       </c>
       <c r="N80">
-        <v>70.34938439999999</v>
+        <v>70.10418419999999</v>
       </c>
       <c r="O80">
-        <v>14.06987688</v>
+        <v>14.02083684</v>
       </c>
       <c r="P80">
-        <v>56.27950752</v>
+        <v>56.08334735999999</v>
       </c>
       <c r="Q80">
-        <v>57.92950751999999</v>
+        <v>57.73334735999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2948052248049857</v>
+        <v>0.3060444586034504</v>
       </c>
       <c r="T80">
-        <v>2.726709272861646</v>
+        <v>2.849783489646194</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.678280786946277</v>
+        <v>4.619062042807717</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09921893630672457</v>
+        <v>0.09907352315635229</v>
       </c>
       <c r="C81">
-        <v>179.2387691281039</v>
+        <v>175.6513452040082</v>
       </c>
       <c r="D81">
-        <v>516.6247691281039</v>
+        <v>517.4713452040082</v>
       </c>
       <c r="E81">
-        <v>150.286</v>
+        <v>154.72</v>
       </c>
       <c r="F81">
-        <v>350.286</v>
+        <v>354.72</v>
       </c>
       <c r="G81">
         <v>12.9</v>
@@ -7929,28 +7929,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M81">
-        <v>19.3708158</v>
+        <v>19.616016</v>
       </c>
       <c r="N81">
-        <v>70.10418419999999</v>
+        <v>69.85898399999999</v>
       </c>
       <c r="O81">
-        <v>14.02083684</v>
+        <v>13.9717968</v>
       </c>
       <c r="P81">
-        <v>56.08334735999999</v>
+        <v>55.88718719999999</v>
       </c>
       <c r="Q81">
-        <v>57.73334735999999</v>
+        <v>57.53718719999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3060444586034504</v>
+        <v>0.3184076157817616</v>
       </c>
       <c r="T81">
-        <v>2.849783489646194</v>
+        <v>2.985165128109196</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.619062042807717</v>
+        <v>4.56132376727262</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09907352315635229</v>
+        <v>0.09892811000598004</v>
       </c>
       <c r="C82">
-        <v>175.6513452040082</v>
+        <v>172.0667003468133</v>
       </c>
       <c r="D82">
-        <v>517.4713452040082</v>
+        <v>518.3207003468133</v>
       </c>
       <c r="E82">
-        <v>154.72</v>
+        <v>159.154</v>
       </c>
       <c r="F82">
-        <v>354.72</v>
+        <v>359.154</v>
       </c>
       <c r="G82">
         <v>12.9</v>
@@ -8011,28 +8011,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M82">
-        <v>19.616016</v>
+        <v>19.8612162</v>
       </c>
       <c r="N82">
-        <v>69.85898399999999</v>
+        <v>69.61378379999999</v>
       </c>
       <c r="O82">
-        <v>13.9717968</v>
+        <v>13.92275676</v>
       </c>
       <c r="P82">
-        <v>55.88718719999999</v>
+        <v>55.69102703999999</v>
       </c>
       <c r="Q82">
-        <v>57.53718719999999</v>
+        <v>57.34102703999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3184076157817616</v>
+        <v>0.3320721579262108</v>
       </c>
       <c r="T82">
-        <v>2.985165128109196</v>
+        <v>3.134797465357777</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.56132376727262</v>
+        <v>4.505011128170489</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09892811000598004</v>
+        <v>0.1004226968556078</v>
       </c>
       <c r="C83">
-        <v>172.0667003468133</v>
+        <v>159.0335900930012</v>
       </c>
       <c r="D83">
-        <v>518.3207003468133</v>
+        <v>509.7215900930013</v>
       </c>
       <c r="E83">
-        <v>159.154</v>
+        <v>163.588</v>
       </c>
       <c r="F83">
-        <v>359.154</v>
+        <v>363.588</v>
       </c>
       <c r="G83">
         <v>12.9</v>
@@ -8093,45 +8093,45 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M83">
-        <v>19.8612162</v>
+        <v>21.0153864</v>
       </c>
       <c r="N83">
-        <v>69.61378379999999</v>
+        <v>68.45961359999998</v>
       </c>
       <c r="O83">
-        <v>13.92275676</v>
+        <v>13.69192272</v>
       </c>
       <c r="P83">
-        <v>55.69102703999999</v>
+        <v>54.76769087999999</v>
       </c>
       <c r="Q83">
-        <v>57.34102703999999</v>
+        <v>56.41769087999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3320721579262108</v>
+        <v>0.3472549825311543</v>
       </c>
       <c r="T83">
-        <v>3.134797465357777</v>
+        <v>3.301055617856201</v>
       </c>
       <c r="U83">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V83">
         <v>0.2</v>
       </c>
       <c r="W83">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.505011128170489</v>
+        <v>4.257594806822109</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1004226968556078</v>
+        <v>0.1002972837052355</v>
       </c>
       <c r="C84">
-        <v>159.0335900930012</v>
+        <v>155.3101732760064</v>
       </c>
       <c r="D84">
-        <v>509.7215900930013</v>
+        <v>510.4321732760064</v>
       </c>
       <c r="E84">
-        <v>163.588</v>
+        <v>168.022</v>
       </c>
       <c r="F84">
-        <v>363.588</v>
+        <v>368.022</v>
       </c>
       <c r="G84">
         <v>12.9</v>
@@ -8175,28 +8175,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M84">
-        <v>21.0153864</v>
+        <v>21.2716716</v>
       </c>
       <c r="N84">
-        <v>68.45961359999998</v>
+        <v>68.20332839999999</v>
       </c>
       <c r="O84">
-        <v>13.69192272</v>
+        <v>13.64066568</v>
       </c>
       <c r="P84">
-        <v>54.76769087999999</v>
+        <v>54.56266271999999</v>
       </c>
       <c r="Q84">
-        <v>56.41769087999999</v>
+        <v>56.21266271999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3472549825311543</v>
+        <v>0.3642240217955031</v>
       </c>
       <c r="T84">
-        <v>3.301055617856201</v>
+        <v>3.486873553001498</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.257594806822109</v>
+        <v>4.206298483848349</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1002972837052355</v>
+        <v>0.1001718705548632</v>
       </c>
       <c r="C85">
-        <v>155.3101732760064</v>
+        <v>151.5887404179166</v>
       </c>
       <c r="D85">
-        <v>510.4321732760064</v>
+        <v>511.1447404179166</v>
       </c>
       <c r="E85">
-        <v>168.022</v>
+        <v>172.456</v>
       </c>
       <c r="F85">
-        <v>368.022</v>
+        <v>372.456</v>
       </c>
       <c r="G85">
         <v>12.9</v>
@@ -8257,28 +8257,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M85">
-        <v>21.2716716</v>
+        <v>21.5279568</v>
       </c>
       <c r="N85">
-        <v>68.20332839999999</v>
+        <v>67.9470432</v>
       </c>
       <c r="O85">
-        <v>13.64066568</v>
+        <v>13.58940864</v>
       </c>
       <c r="P85">
-        <v>54.56266271999999</v>
+        <v>54.35763455999999</v>
       </c>
       <c r="Q85">
-        <v>56.21266271999999</v>
+        <v>56.00763455999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3642240217955031</v>
+        <v>0.3833141909678954</v>
       </c>
       <c r="T85">
-        <v>3.486873553001498</v>
+        <v>3.695918730039958</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.206298483848349</v>
+        <v>4.156223501897774</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1001718705548632</v>
+        <v>0.100046457404491</v>
       </c>
       <c r="C86">
-        <v>151.5887404179167</v>
+        <v>147.8692998392119</v>
       </c>
       <c r="D86">
-        <v>511.1447404179166</v>
+        <v>511.8592998392118</v>
       </c>
       <c r="E86">
-        <v>172.456</v>
+        <v>176.89</v>
       </c>
       <c r="F86">
-        <v>372.456</v>
+        <v>376.89</v>
       </c>
       <c r="G86">
         <v>12.9</v>
@@ -8339,28 +8339,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M86">
-        <v>21.5279568</v>
+        <v>21.784242</v>
       </c>
       <c r="N86">
-        <v>67.9470432</v>
+        <v>67.69075799999999</v>
       </c>
       <c r="O86">
-        <v>13.58940864</v>
+        <v>13.5381516</v>
       </c>
       <c r="P86">
-        <v>54.35763455999999</v>
+        <v>54.15260639999999</v>
       </c>
       <c r="Q86">
-        <v>56.00763455999999</v>
+        <v>55.80260639999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3833141909678952</v>
+        <v>0.4049497160299397</v>
       </c>
       <c r="T86">
-        <v>3.695918730039955</v>
+        <v>3.932836597350209</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.156223501897774</v>
+        <v>4.107326754816623</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.100046457404491</v>
+        <v>0.0999210442541187</v>
       </c>
       <c r="C87">
-        <v>147.8692998392119</v>
+        <v>144.1518599069641</v>
       </c>
       <c r="D87">
-        <v>511.8592998392118</v>
+        <v>512.5758599069641</v>
       </c>
       <c r="E87">
-        <v>176.89</v>
+        <v>181.324</v>
       </c>
       <c r="F87">
-        <v>376.89</v>
+        <v>381.324</v>
       </c>
       <c r="G87">
         <v>12.9</v>
@@ -8421,28 +8421,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M87">
-        <v>21.784242</v>
+        <v>22.0405272</v>
       </c>
       <c r="N87">
-        <v>67.69075799999999</v>
+        <v>67.43447279999999</v>
       </c>
       <c r="O87">
-        <v>13.5381516</v>
+        <v>13.48689456</v>
       </c>
       <c r="P87">
-        <v>54.15260639999999</v>
+        <v>53.94757824</v>
       </c>
       <c r="Q87">
-        <v>55.80260639999999</v>
+        <v>55.59757824</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4049497160299397</v>
+        <v>0.4296760303865621</v>
       </c>
       <c r="T87">
-        <v>3.932836597350209</v>
+        <v>4.203599874276214</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.107326754816623</v>
+        <v>4.059567141388523</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0999210442541187</v>
+        <v>0.09979563110374644</v>
       </c>
       <c r="C88">
-        <v>144.1518599069641</v>
+        <v>140.4364290351636</v>
       </c>
       <c r="D88">
-        <v>512.5758599069641</v>
+        <v>513.2944290351636</v>
       </c>
       <c r="E88">
-        <v>181.324</v>
+        <v>185.758</v>
       </c>
       <c r="F88">
-        <v>381.324</v>
+        <v>385.758</v>
       </c>
       <c r="G88">
         <v>12.9</v>
@@ -8503,28 +8503,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M88">
-        <v>22.0405272</v>
+        <v>22.2968124</v>
       </c>
       <c r="N88">
-        <v>67.43447279999999</v>
+        <v>67.1781876</v>
       </c>
       <c r="O88">
-        <v>13.48689456</v>
+        <v>13.43563752</v>
       </c>
       <c r="P88">
-        <v>53.94757824</v>
+        <v>53.74255008</v>
       </c>
       <c r="Q88">
-        <v>55.59757824</v>
+        <v>55.39255008</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4296760303865621</v>
+        <v>0.4582063931057418</v>
       </c>
       <c r="T88">
-        <v>4.203599874276214</v>
+        <v>4.516019039960065</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.059567141388523</v>
+        <v>4.012905450108196</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09979563110374644</v>
+        <v>0.1021342179533742</v>
       </c>
       <c r="C89">
-        <v>140.4364290351636</v>
+        <v>122.9262644980355</v>
       </c>
       <c r="D89">
-        <v>513.2944290351636</v>
+        <v>500.2182644980355</v>
       </c>
       <c r="E89">
-        <v>185.758</v>
+        <v>190.192</v>
       </c>
       <c r="F89">
-        <v>385.758</v>
+        <v>390.192</v>
       </c>
       <c r="G89">
         <v>12.9</v>
@@ -8585,45 +8585,45 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M89">
-        <v>22.2968124</v>
+        <v>23.9187696</v>
       </c>
       <c r="N89">
-        <v>67.1781876</v>
+        <v>65.55623039999999</v>
       </c>
       <c r="O89">
-        <v>13.43563752</v>
+        <v>13.11124608</v>
       </c>
       <c r="P89">
-        <v>53.74255008</v>
+        <v>52.44498431999999</v>
       </c>
       <c r="Q89">
-        <v>55.39255008</v>
+        <v>54.09498431999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4582063931057418</v>
+        <v>0.491491816278118</v>
       </c>
       <c r="T89">
-        <v>4.516019039960065</v>
+        <v>4.880508066591224</v>
       </c>
       <c r="U89">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V89">
         <v>0.2</v>
       </c>
       <c r="W89">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>4.012905450108196</v>
+        <v>3.740786064513953</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1021342179533742</v>
+        <v>0.1020368048030019</v>
       </c>
       <c r="C90">
-        <v>122.9262644980355</v>
+        <v>119.0236363610319</v>
       </c>
       <c r="D90">
-        <v>500.2182644980355</v>
+        <v>500.7496363610318</v>
       </c>
       <c r="E90">
-        <v>190.192</v>
+        <v>194.626</v>
       </c>
       <c r="F90">
-        <v>390.192</v>
+        <v>394.626</v>
       </c>
       <c r="G90">
         <v>12.9</v>
@@ -8667,28 +8667,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M90">
-        <v>23.9187696</v>
+        <v>24.1905738</v>
       </c>
       <c r="N90">
-        <v>65.55623039999999</v>
+        <v>65.2844262</v>
       </c>
       <c r="O90">
-        <v>13.11124608</v>
+        <v>13.05688524</v>
       </c>
       <c r="P90">
-        <v>52.44498431999999</v>
+        <v>52.22754096</v>
       </c>
       <c r="Q90">
-        <v>54.09498431999999</v>
+        <v>53.87754096</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.491491816278118</v>
+        <v>0.5308291345727445</v>
       </c>
       <c r="T90">
-        <v>4.880508066591224</v>
+        <v>5.31126782533714</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.740786064513953</v>
+        <v>3.698754760418292</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1020368048030019</v>
+        <v>0.1019393916526296</v>
       </c>
       <c r="C91">
-        <v>119.0236363610319</v>
+        <v>115.1221383559604</v>
       </c>
       <c r="D91">
-        <v>500.7496363610318</v>
+        <v>501.2821383559605</v>
       </c>
       <c r="E91">
-        <v>194.626</v>
+        <v>199.06</v>
       </c>
       <c r="F91">
-        <v>394.626</v>
+        <v>399.06</v>
       </c>
       <c r="G91">
         <v>12.9</v>
@@ -8749,28 +8749,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M91">
-        <v>24.1905738</v>
+        <v>24.462378</v>
       </c>
       <c r="N91">
-        <v>65.2844262</v>
+        <v>65.01262199999999</v>
       </c>
       <c r="O91">
-        <v>13.05688524</v>
+        <v>13.0025244</v>
       </c>
       <c r="P91">
-        <v>52.22754096</v>
+        <v>52.01009759999999</v>
       </c>
       <c r="Q91">
-        <v>53.87754096</v>
+        <v>53.66009759999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5308291345727445</v>
+        <v>0.5780339165262964</v>
       </c>
       <c r="T91">
-        <v>5.31126782533714</v>
+        <v>5.82817953583224</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.698754760418292</v>
+        <v>3.657657485302532</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1019393916526296</v>
+        <v>0.1018419785022574</v>
       </c>
       <c r="C92">
-        <v>115.1221383559604</v>
+        <v>111.2217740920393</v>
       </c>
       <c r="D92">
-        <v>501.2821383559605</v>
+        <v>501.8157740920392</v>
       </c>
       <c r="E92">
-        <v>199.06</v>
+        <v>203.494</v>
       </c>
       <c r="F92">
-        <v>399.06</v>
+        <v>403.494</v>
       </c>
       <c r="G92">
         <v>12.9</v>
@@ -8831,28 +8831,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M92">
-        <v>24.462378</v>
+        <v>24.7341822</v>
       </c>
       <c r="N92">
-        <v>65.01262199999999</v>
+        <v>64.7408178</v>
       </c>
       <c r="O92">
-        <v>13.0025244</v>
+        <v>12.94816356</v>
       </c>
       <c r="P92">
-        <v>52.01009759999999</v>
+        <v>51.79265424</v>
       </c>
       <c r="Q92">
-        <v>53.66009759999999</v>
+        <v>53.44265424</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5780339165262964</v>
+        <v>0.6357286500250819</v>
       </c>
       <c r="T92">
-        <v>5.82817953583224</v>
+        <v>6.45996051532625</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.657657485302532</v>
+        <v>3.617463447002505</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1018419785022574</v>
+        <v>0.1017445653518851</v>
       </c>
       <c r="C93">
-        <v>111.2217740920393</v>
+        <v>107.3225471938707</v>
       </c>
       <c r="D93">
-        <v>501.8157740920392</v>
+        <v>502.3505471938707</v>
       </c>
       <c r="E93">
-        <v>203.494</v>
+        <v>207.928</v>
       </c>
       <c r="F93">
-        <v>403.494</v>
+        <v>407.928</v>
       </c>
       <c r="G93">
         <v>12.9</v>
@@ -8913,28 +8913,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M93">
-        <v>24.7341822</v>
+        <v>25.0059864</v>
       </c>
       <c r="N93">
-        <v>64.7408178</v>
+        <v>64.4690136</v>
       </c>
       <c r="O93">
-        <v>12.94816356</v>
+        <v>12.89380272</v>
       </c>
       <c r="P93">
-        <v>51.79265424</v>
+        <v>51.57521088</v>
       </c>
       <c r="Q93">
-        <v>53.44265424</v>
+        <v>53.22521088</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6357286500250819</v>
+        <v>0.707847066898564</v>
       </c>
       <c r="T93">
-        <v>6.45996051532625</v>
+        <v>7.249686739693765</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.617463447002505</v>
+        <v>3.578143192143782</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1017445653518851</v>
+        <v>0.1016471522015128</v>
       </c>
       <c r="C94">
-        <v>107.3225471938707</v>
+        <v>103.4244613015249</v>
       </c>
       <c r="D94">
-        <v>502.3505471938707</v>
+        <v>502.8864613015249</v>
       </c>
       <c r="E94">
-        <v>207.928</v>
+        <v>212.362</v>
       </c>
       <c r="F94">
-        <v>407.928</v>
+        <v>412.362</v>
       </c>
       <c r="G94">
         <v>12.9</v>
@@ -8995,28 +8995,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M94">
-        <v>25.0059864</v>
+        <v>25.2777906</v>
       </c>
       <c r="N94">
-        <v>64.4690136</v>
+        <v>64.19720939999999</v>
       </c>
       <c r="O94">
-        <v>12.89380272</v>
+        <v>12.83944188</v>
       </c>
       <c r="P94">
-        <v>51.57521088</v>
+        <v>51.35776752</v>
       </c>
       <c r="Q94">
-        <v>53.22521088</v>
+        <v>53.00776751999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.707847066898564</v>
+        <v>0.800570745735898</v>
       </c>
       <c r="T94">
-        <v>7.249686739693765</v>
+        <v>8.265049028166281</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.578143192143782</v>
+        <v>3.539668534163741</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1016471522015128</v>
+        <v>0.1015497390511406</v>
       </c>
       <c r="C95">
-        <v>103.4244613015249</v>
+        <v>99.52752007062128</v>
       </c>
       <c r="D95">
-        <v>502.8864613015249</v>
+        <v>503.4235200706212</v>
       </c>
       <c r="E95">
-        <v>212.362</v>
+        <v>216.796</v>
       </c>
       <c r="F95">
-        <v>412.362</v>
+        <v>416.796</v>
       </c>
       <c r="G95">
         <v>12.9</v>
@@ -9077,28 +9077,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M95">
-        <v>25.2777906</v>
+        <v>25.5495948</v>
       </c>
       <c r="N95">
-        <v>64.19720939999999</v>
+        <v>63.92540519999999</v>
       </c>
       <c r="O95">
-        <v>12.83944188</v>
+        <v>12.78508104</v>
       </c>
       <c r="P95">
-        <v>51.35776752</v>
+        <v>51.14032415999999</v>
       </c>
       <c r="Q95">
-        <v>53.00776751999999</v>
+        <v>52.79032415999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.800570745735898</v>
+        <v>0.9242023175190101</v>
       </c>
       <c r="T95">
-        <v>8.265049028166281</v>
+        <v>9.618865412796305</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.539668534163741</v>
+        <v>3.502012485927957</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1015497390511406</v>
+        <v>0.1035803259007683</v>
       </c>
       <c r="C96">
-        <v>99.52752007062128</v>
+        <v>84.13057305725744</v>
       </c>
       <c r="D96">
-        <v>503.4235200706212</v>
+        <v>492.4605730572575</v>
       </c>
       <c r="E96">
-        <v>216.796</v>
+        <v>221.23</v>
       </c>
       <c r="F96">
-        <v>416.796</v>
+        <v>421.23</v>
       </c>
       <c r="G96">
         <v>12.9</v>
@@ -9159,45 +9159,45 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M96">
-        <v>25.5495948</v>
+        <v>27.000843</v>
       </c>
       <c r="N96">
-        <v>63.92540519999999</v>
+        <v>62.47415699999999</v>
       </c>
       <c r="O96">
-        <v>12.78508104</v>
+        <v>12.4948314</v>
       </c>
       <c r="P96">
-        <v>51.14032415999999</v>
+        <v>49.9793256</v>
       </c>
       <c r="Q96">
-        <v>52.79032415999999</v>
+        <v>51.62932559999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9242023175190101</v>
+        <v>1.097286518015367</v>
       </c>
       <c r="T96">
-        <v>9.618865412796305</v>
+        <v>11.51420835127834</v>
       </c>
       <c r="U96">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V96">
         <v>0.2</v>
       </c>
       <c r="W96">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.502012485927957</v>
+        <v>3.313785425143948</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1035803259007683</v>
+        <v>0.103505312750396</v>
       </c>
       <c r="C97">
-        <v>84.13057305725744</v>
+        <v>80.09306159109002</v>
       </c>
       <c r="D97">
-        <v>492.4605730572575</v>
+        <v>492.85706159109</v>
       </c>
       <c r="E97">
-        <v>221.23</v>
+        <v>225.664</v>
       </c>
       <c r="F97">
-        <v>421.23</v>
+        <v>425.664</v>
       </c>
       <c r="G97">
         <v>12.9</v>
@@ -9241,28 +9241,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M97">
-        <v>27.000843</v>
+        <v>27.2850624</v>
       </c>
       <c r="N97">
-        <v>62.47415699999999</v>
+        <v>62.18993759999999</v>
       </c>
       <c r="O97">
-        <v>12.4948314</v>
+        <v>12.43798752</v>
       </c>
       <c r="P97">
-        <v>49.9793256</v>
+        <v>49.75195007999999</v>
       </c>
       <c r="Q97">
-        <v>51.62932559999999</v>
+        <v>51.40195007999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.097286518015367</v>
+        <v>1.356912818759903</v>
       </c>
       <c r="T97">
-        <v>11.51420835127834</v>
+        <v>14.3572227590014</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.313785425143948</v>
+        <v>3.279266826965365</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.103505312750396</v>
+        <v>0.1034302996000238</v>
       </c>
       <c r="C98">
-        <v>80.09306159109002</v>
+        <v>76.05618907892233</v>
       </c>
       <c r="D98">
-        <v>492.85706159109</v>
+        <v>493.2541890789223</v>
       </c>
       <c r="E98">
-        <v>225.664</v>
+        <v>230.098</v>
       </c>
       <c r="F98">
-        <v>425.664</v>
+        <v>430.098</v>
       </c>
       <c r="G98">
         <v>12.9</v>
@@ -9323,28 +9323,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M98">
-        <v>27.2850624</v>
+        <v>27.5692818</v>
       </c>
       <c r="N98">
-        <v>62.18993759999999</v>
+        <v>61.9057182</v>
       </c>
       <c r="O98">
-        <v>12.43798752</v>
+        <v>12.38114364</v>
       </c>
       <c r="P98">
-        <v>49.75195007999999</v>
+        <v>49.52457456</v>
       </c>
       <c r="Q98">
-        <v>51.40195007999999</v>
+        <v>51.17457456</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.3569128187599</v>
+        <v>1.78962332000079</v>
       </c>
       <c r="T98">
-        <v>14.35722275900136</v>
+        <v>19.09558010520642</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.279266826965365</v>
+        <v>3.245459952460568</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1034302996000238</v>
+        <v>0.1033552864496515</v>
       </c>
       <c r="C99">
-        <v>76.05618907892233</v>
+        <v>72.01995706654208</v>
       </c>
       <c r="D99">
-        <v>493.2541890789223</v>
+        <v>493.6519570665421</v>
       </c>
       <c r="E99">
-        <v>230.098</v>
+        <v>234.532</v>
       </c>
       <c r="F99">
-        <v>430.098</v>
+        <v>434.532</v>
       </c>
       <c r="G99">
         <v>12.9</v>
@@ -9405,28 +9405,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M99">
-        <v>27.5692818</v>
+        <v>27.8535012</v>
       </c>
       <c r="N99">
-        <v>61.9057182</v>
+        <v>61.6214988</v>
       </c>
       <c r="O99">
-        <v>12.38114364</v>
+        <v>12.32429976</v>
       </c>
       <c r="P99">
-        <v>49.52457456</v>
+        <v>49.29719904</v>
       </c>
       <c r="Q99">
-        <v>51.17457456</v>
+        <v>50.94719903999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.78962332000079</v>
+        <v>2.655044322482572</v>
       </c>
       <c r="T99">
-        <v>19.09558010520642</v>
+        <v>28.57229479761656</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.245459952460568</v>
+        <v>3.212343014170154</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1033552864496515</v>
+        <v>0.1032802732992792</v>
       </c>
       <c r="C100">
-        <v>72.01995706654208</v>
+        <v>67.9843671047276</v>
       </c>
       <c r="D100">
-        <v>493.6519570665421</v>
+        <v>494.0503671047276</v>
       </c>
       <c r="E100">
-        <v>234.532</v>
+        <v>238.966</v>
       </c>
       <c r="F100">
-        <v>434.532</v>
+        <v>438.966</v>
       </c>
       <c r="G100">
         <v>12.9</v>
@@ -9487,28 +9487,28 @@
         <v>89.47499999999999</v>
       </c>
       <c r="M100">
-        <v>27.8535012</v>
+        <v>28.1377206</v>
       </c>
       <c r="N100">
-        <v>61.6214988</v>
+        <v>61.3372794</v>
       </c>
       <c r="O100">
-        <v>12.32429976</v>
+        <v>12.26745588</v>
       </c>
       <c r="P100">
-        <v>49.29719904</v>
+        <v>49.06982352</v>
       </c>
       <c r="Q100">
-        <v>50.94719903999999</v>
+        <v>50.71982352</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.655044322482572</v>
+        <v>5.251307329927918</v>
       </c>
       <c r="T100">
-        <v>28.57229479761656</v>
+        <v>57.00243887484697</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.212343014170154</v>
+        <v>3.179895104936112</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1032802732992792</v>
-      </c>
-      <c r="C101">
-        <v>67.9843671047276</v>
-      </c>
-      <c r="D101">
-        <v>494.0503671047276</v>
-      </c>
-      <c r="E101">
-        <v>238.966</v>
-      </c>
-      <c r="F101">
-        <v>438.966</v>
-      </c>
-      <c r="G101">
-        <v>12.9</v>
-      </c>
-      <c r="H101">
-        <v>243.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>91.125</v>
-      </c>
-      <c r="K101">
-        <v>1.65</v>
-      </c>
-      <c r="L101">
-        <v>89.47499999999999</v>
-      </c>
-      <c r="M101">
-        <v>28.1377206</v>
-      </c>
-      <c r="N101">
-        <v>61.3372794</v>
-      </c>
-      <c r="O101">
-        <v>12.26745588</v>
-      </c>
-      <c r="P101">
-        <v>49.06982352</v>
-      </c>
-      <c r="Q101">
-        <v>50.71982352</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.251307329927918</v>
-      </c>
-      <c r="T101">
-        <v>57.00243887484697</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.05128000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.179895104936112</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
